--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.6.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.6.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -1031,7 +1031,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.6.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.6.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y112"/>
+  <dimension ref="A1:Y146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -617,16 +617,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L103: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: å�§</t>
+          <t>L103: stray/suspicious non-ASCII glyph(s): U+5427 CJK UNIFIED IDEOGRAPH-5427 | isolated marker/symbol line :: 吧</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L23: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: 1 â€¢ tor. Conveyancer, etc. Office-23 James</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]HAMILTON EVENING TIMES, FRIDAY, JUNE 29, 1894.</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]HAMILTON EVENING TIMES, FRIDAY, JUNE 29, 1894.</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L83: isolated marker/symbol line :: A</t>
@@ -639,7 +643,7 @@
       </c>
       <c r="P2" s="1" t="inlineStr">
         <is>
-          <t>L234: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: Daily, payable monthly to collector.â€¦...</t>
+          <t>L234: punctuation artifact: repeated periods :: Daily, payable monthly to collector.…...</t>
         </is>
       </c>
       <c r="Q2" s="1" t="inlineStr">
@@ -681,7 +685,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>1480</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
@@ -708,19 +712,19 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L234: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: Daily, payable monthly to collector.â€¦...</t>
+          <t>L104: stray/suspicious non-ASCII glyph(s): U+4E5F CJK UNIFIED IDEOGRAPH-4E5F | isolated marker/symbol line :: 也</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L38: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: N. B.â€”Money to loan on real estate.</t>
+          <t>L23: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: 1 • tor. Conveyancer, etc. Office-23 James</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L103: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: å�§</t>
+          <t>L103: stray/suspicious non-ASCII glyph(s): U+5427 CJK UNIFIED IDEOGRAPH-5427 | isolated marker/symbol line :: 吧</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
@@ -767,7 +771,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>5694</t>
+          <t>5693</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
@@ -799,19 +803,19 @@
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L372: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: New York Board of Health â€” Applicable tary, said the Government declined to</t>
+          <t>L155: stray/suspicious non-ASCII glyph(s): U+2192 RIGHTWARDS ARROW | isolated marker/symbol line :: →</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L71: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: terms of repayment. Officeâ€”No. 8 Main</t>
+          <t>L382: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L148: isolated marker/symbol line :: 6</t>
+          <t>L104: stray/suspicious non-ASCII glyph(s): U+4E5F CJK UNIFIED IDEOGRAPH-4E5F | isolated marker/symbol line :: 也</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
@@ -858,12 +862,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>235</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>136</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
@@ -890,24 +894,24 @@
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L430: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
+          <t>L156: stray/suspicious non-ASCII glyph(s): U+2192 RIGHTWARDS ARROW | isolated marker/symbol line :: →</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L94: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: London, June 28.â€”In the House of</t>
+          <t>L623: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: repeated periods :: Accom.................•</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L155: isolated marker/symbol line :: â†’</t>
+          <t>L148: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L382: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L382: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr">
@@ -977,19 +981,19 @@
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L839: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€ 9.20</t>
+          <t>L303: stray/suspicious non-ASCII glyph(s): U+5382 CJK UNIFIED IDEOGRAPH-5382, U+56FD CJK UNIFIED IDEOGRAPH-56FD :: 厂 国</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L138: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Mr. Leightonâ€”" Is not excessive tea</t>
+          <t>L905: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: '• Thank you," he responded, accepting</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L156: isolated marker/symbol line :: â†’</t>
+          <t>L155: stray/suspicious non-ASCII glyph(s): U+2192 RIGHTWARDS ARROW | isolated marker/symbol line :: →</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
@@ -1022,7 +1026,7 @@
       </c>
       <c r="W6" s="1" t="inlineStr">
         <is>
-          <t>L763: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | abbreviation/spacing may be garbled :: 2 to 5 p.m. Dr. Batesâ€™ residence. No. 53 Augusta</t>
+          <t>L763: abbreviation/spacing may be garbled :: 2 to 5 p.m. Dr. Bates’ residence. No. 53 Augusta</t>
         </is>
       </c>
       <c r="X6" s="1" t="inlineStr"/>
@@ -1064,19 +1068,19 @@
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>L843: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
+          <t>L430: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
         </is>
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L143: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Mr. Morleyâ€”" I must confine myself en-</t>
+          <t>L1171: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • materials, we will offer Dress Goods•</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L169: isolated marker/symbol line :: ,</t>
+          <t>L156: stray/suspicious non-ASCII glyph(s): U+2192 RIGHTWARDS ARROW | isolated marker/symbol line :: →</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
@@ -1151,19 +1155,19 @@
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>L848: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
+          <t>L472: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L168: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: pareilâ€”12 lines to the inch.</t>
+          <t>L1172: stray/suspicious non-ASCII glyph(s): U+2022 BULLET, U+25BA BLACK RIGHT-POINTING POINTER :: •►at the cost price and in some instances 1,</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L233: symbol-only separator/garbage line :: $3 00</t>
+          <t>L169: isolated marker/symbol line :: ,</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
@@ -1238,19 +1242,19 @@
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>L861: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
+          <t>L627: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L234: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: How to Save the Spark of Lifeâ€”A Set of</t>
+          <t>L1173: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: $at even less than what we paid for•</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L235: isolated marker/symbol line :: 25</t>
+          <t>L233: symbol-only separator/garbage line :: $3 00</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr">
@@ -1271,7 +1275,7 @@
       <c r="R9" s="1" t="inlineStr"/>
       <c r="S9" s="1" t="inlineStr">
         <is>
-          <t>L1182: line starts with punctuation glued to text | suspicious token(s): Dress2 (letter/digit mix) :: *All light shades in Woolen Dress2</t>
+          <t>L1171: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • materials, we will offer Dress Goods•</t>
         </is>
       </c>
       <c r="T9" s="1" t="inlineStr"/>
@@ -1297,12 +1301,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1325,19 +1329,19 @@
       </c>
       <c r="J10" s="1" t="inlineStr">
         <is>
-          <t>L867: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
+          <t>L704: stray/suspicious non-ASCII glyph(s): U+4EA7 CJK UNIFIED IDEOGRAPH-4EA7 | isolated marker/symbol line :: 产</t>
         </is>
       </c>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L294: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: beryâ€™s remarks by stating that the pres-</t>
+          <t>L1174: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •them.•</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L237: symbol-only separator/garbage line :: 1 00</t>
+          <t>L235: isolated marker/symbol line :: 25</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr">
@@ -1356,7 +1360,11 @@
         </is>
       </c>
       <c r="R10" s="1" t="inlineStr"/>
-      <c r="S10" s="1" t="inlineStr"/>
+      <c r="S10" s="1" t="inlineStr">
+        <is>
+          <t>L1174: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •them.•</t>
+        </is>
+      </c>
       <c r="T10" s="1" t="inlineStr"/>
       <c r="U10" s="1" t="inlineStr"/>
       <c r="V10" s="1" t="inlineStr">
@@ -1385,7 +1393,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1403,24 +1411,24 @@
       </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
-          <t>L762: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 9a (letter/digit mix) :: street, Toronto. Office hour â€”9a. m. tolp.Â».,</t>
+          <t>L762: suspicious token(s): 9a (letter/digit mix) :: street, Toronto. Office hour —9a. m. tolp.».,</t>
         </is>
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
-          <t>L868: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
+          <t>L772: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>L298: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Billâ€”Immigrant Drowned-Attempt to</t>
+          <t>L1175: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text | suspicious token(s): 25c (letter/digit mix), 28c (letter/digit mix), 30c (letter/digit mix) :: •The balance of the 25c, 28c and 30c$</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L266: isolated marker/symbol line :: B</t>
+          <t>L237: symbol-only separator/garbage line :: 1 00</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
@@ -1439,7 +1447,11 @@
         </is>
       </c>
       <c r="R11" s="1" t="inlineStr"/>
-      <c r="S11" s="1" t="inlineStr"/>
+      <c r="S11" s="1" t="inlineStr">
+        <is>
+          <t>L1175: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text | suspicious token(s): 25c (letter/digit mix), 28c (letter/digit mix), 30c (letter/digit mix) :: •The balance of the 25c, 28c and 30c$</t>
+        </is>
+      </c>
       <c r="T11" s="1" t="inlineStr"/>
       <c r="U11" s="1" t="inlineStr"/>
       <c r="V11" s="1" t="inlineStr">
@@ -1449,7 +1461,7 @@
       </c>
       <c r="W11" s="1" t="inlineStr">
         <is>
-          <t>L1074: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | abbreviation/spacing may be garbled :: From Dundas.â€”6.10, 8.00. 9.00, 10 15, 11.15 a.m.,</t>
+          <t>L1074: abbreviation/spacing may be garbled :: From Dundas.—6.10, 8.00. 9.00, 10 15, 11.15 a.m.,</t>
         </is>
       </c>
       <c r="X11" s="1" t="inlineStr"/>
@@ -1463,12 +1475,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>145</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1491,19 +1503,19 @@
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
-          <t>L871: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
+          <t>L840: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>L316: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Casimir-Perierâ€™s</t>
+          <t>L1177: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | suspicious token(s): 30c (letter/digit mix) :: $All that's left of the 30c All-wool•</t>
         </is>
       </c>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L271: isolated marker/symbol line :: 55</t>
+          <t>L266: isolated marker/symbol line :: B</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
@@ -1522,7 +1534,11 @@
         </is>
       </c>
       <c r="R12" s="1" t="inlineStr"/>
-      <c r="S12" s="1" t="inlineStr"/>
+      <c r="S12" s="1" t="inlineStr">
+        <is>
+          <t>L1178: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Delaines at 19%ca yard.$</t>
+        </is>
+      </c>
       <c r="T12" s="1" t="inlineStr"/>
       <c r="U12" s="1" t="inlineStr"/>
       <c r="V12" s="1" t="inlineStr">
@@ -1570,19 +1586,19 @@
       </c>
       <c r="J13" s="1" t="inlineStr">
         <is>
-          <t>L872: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
+          <t>L853: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>L341: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Barnardoâ€™s home started from Lottion</t>
+          <t>L1178: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Delaines at 19%ca yard.$</t>
         </is>
       </c>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L283: isolated marker/symbol line :: T.</t>
+          <t>L271: isolated marker/symbol line :: 55</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
@@ -1597,7 +1613,11 @@
         </is>
       </c>
       <c r="R13" s="1" t="inlineStr"/>
-      <c r="S13" s="1" t="inlineStr"/>
+      <c r="S13" s="1" t="inlineStr">
+        <is>
+          <t>L1181: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • All Spotted White Muslins at cost.X</t>
+        </is>
+      </c>
       <c r="T13" s="1" t="inlineStr"/>
       <c r="U13" s="1" t="inlineStr"/>
       <c r="V13" s="1" t="inlineStr">
@@ -1622,7 +1642,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1645,19 +1665,19 @@
       </c>
       <c r="J14" s="1" t="inlineStr">
         <is>
-          <t>L878: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
+          <t>L860: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>L355: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: M. Casimir-Perierâ€™s election is an augury</t>
+          <t>L1180: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | suspicious token(s): 25c (letter/digit mix) :: %25c a yard.•</t>
         </is>
       </c>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L288: isolated marker/symbol line :: L</t>
+          <t>L283: isolated marker/symbol line :: T.</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
@@ -1672,7 +1692,11 @@
         </is>
       </c>
       <c r="R14" s="1" t="inlineStr"/>
-      <c r="S14" s="1" t="inlineStr"/>
+      <c r="S14" s="1" t="inlineStr">
+        <is>
+          <t>L1182: line starts with punctuation glued to text | suspicious token(s): Dress2 (letter/digit mix) :: *All light shades in Woolen Dress2</t>
+        </is>
+      </c>
       <c r="T14" s="1" t="inlineStr"/>
       <c r="U14" s="1" t="inlineStr"/>
       <c r="V14" s="1" t="inlineStr">
@@ -1720,19 +1744,19 @@
       </c>
       <c r="J15" s="1" t="inlineStr">
         <is>
-          <t>L879: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
+          <t>L864: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="K15" s="1" t="inlineStr">
         <is>
-          <t>L375: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Yesterdayâ€™s session of the United States</t>
+          <t>L1181: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • All Spotted White Muslins at cost.X</t>
         </is>
       </c>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L296: isolated marker/symbol line :: C.</t>
+          <t>L288: isolated marker/symbol line :: L</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
@@ -1747,7 +1771,11 @@
         </is>
       </c>
       <c r="R15" s="1" t="inlineStr"/>
-      <c r="S15" s="1" t="inlineStr"/>
+      <c r="S15" s="1" t="inlineStr">
+        <is>
+          <t>L1184: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •The choice of the balance of our•</t>
+        </is>
+      </c>
       <c r="T15" s="1" t="inlineStr"/>
       <c r="U15" s="1" t="inlineStr"/>
       <c r="V15" s="1" t="inlineStr">
@@ -1790,24 +1818,24 @@
       </c>
       <c r="I16" s="1" t="inlineStr">
         <is>
-          <t>L1175: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | suspicious token(s): 25c (letter/digit mix), 28c (letter/digit mix), 30c (letter/digit mix) :: â€¢The balance of the 25c, 28c and 30c$</t>
+          <t>L1175: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text | suspicious token(s): 25c (letter/digit mix), 28c (letter/digit mix), 30c (letter/digit mix) :: •The balance of the 25c, 28c and 30c$</t>
         </is>
       </c>
       <c r="J16" s="1" t="inlineStr">
         <is>
-          <t>L881: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
+          <t>L874: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="K16" s="1" t="inlineStr">
         <is>
-          <t>L382: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L1183: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: $Materials at cost and under.•</t>
         </is>
       </c>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L302: isolated marker/symbol line :: M</t>
+          <t>L296: isolated marker/symbol line :: C.</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
@@ -1822,7 +1850,11 @@
         </is>
       </c>
       <c r="R16" s="1" t="inlineStr"/>
-      <c r="S16" s="1" t="inlineStr"/>
+      <c r="S16" s="1" t="inlineStr">
+        <is>
+          <t>L1187: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text | suspicious token(s): 40c (letter/digit mix) :: • 40c a yard. .•</t>
+        </is>
+      </c>
       <c r="T16" s="1" t="inlineStr"/>
       <c r="U16" s="1" t="inlineStr"/>
       <c r="V16" s="1" t="inlineStr">
@@ -1870,19 +1902,19 @@
       </c>
       <c r="J17" s="1" t="inlineStr">
         <is>
-          <t>L882: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
+          <t>L895: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="K17" s="1" t="inlineStr">
         <is>
-          <t>L432: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE, U+2122 TRADE MARK SIGN :: may say â€˜Rot,â€™" continued Mr. Keir</t>
+          <t>L1184: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •The choice of the balance of our•</t>
         </is>
       </c>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L307: isolated marker/symbol line :: &amp;</t>
+          <t>L302: isolated marker/symbol line :: M</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
@@ -1893,11 +1925,15 @@
       <c r="P17" s="1" t="inlineStr"/>
       <c r="Q17" s="1" t="inlineStr">
         <is>
-          <t>L623: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: repeated periods :: Accom.................â€¢</t>
+          <t>L623: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: repeated periods :: Accom.................•</t>
         </is>
       </c>
       <c r="R17" s="1" t="inlineStr"/>
-      <c r="S17" s="1" t="inlineStr"/>
+      <c r="S17" s="1" t="inlineStr">
+        <is>
+          <t>L1194: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text | suspicious token(s): 59c (letter/digit mix) :: • colors, at 59c each. •</t>
+        </is>
+      </c>
       <c r="T17" s="1" t="inlineStr"/>
       <c r="U17" s="1" t="inlineStr"/>
       <c r="V17" s="1" t="inlineStr">
@@ -1928,24 +1964,24 @@
       </c>
       <c r="I18" s="1" t="inlineStr">
         <is>
-          <t>L1177: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | suspicious token(s): 30c (letter/digit mix) :: $All that's left of the 30c All-woolâ€¢</t>
+          <t>L1177: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | suspicious token(s): 30c (letter/digit mix) :: $All that's left of the 30c All-wool•</t>
         </is>
       </c>
       <c r="J18" s="1" t="inlineStr">
         <is>
-          <t>L901: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
+          <t>L904: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="K18" s="1" t="inlineStr">
         <is>
-          <t>L484: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: GEORGE LYNCH-STAUNTON, Arthur Oâ€™HEIR.</t>
+          <t>L1185: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: 1• latest and very stylish Dress Materials,$</t>
         </is>
       </c>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L308: isolated marker/symbol line :: &amp;</t>
+          <t>L307: isolated marker/symbol line :: &amp;</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
@@ -1960,7 +1996,11 @@
         </is>
       </c>
       <c r="R18" s="1" t="inlineStr"/>
-      <c r="S18" s="1" t="inlineStr"/>
+      <c r="S18" s="1" t="inlineStr">
+        <is>
+          <t>L1196: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text | suspicious token(s): 75c (letter/digit mix) :: • Ladies’ Umbrellas at 75c each. *</t>
+        </is>
+      </c>
       <c r="T18" s="1" t="inlineStr"/>
       <c r="U18" s="1" t="inlineStr"/>
       <c r="V18" s="1" t="inlineStr">
@@ -1992,19 +2032,19 @@
       </c>
       <c r="J19" s="1" t="inlineStr">
         <is>
-          <t>L908: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
+          <t>L1243: stray/suspicious non-ASCII glyph(s): U+5BB6 CJK UNIFIED IDEOGRAPH-5BB6 | isolated marker/symbol line :: 家</t>
         </is>
       </c>
       <c r="K19" s="1" t="inlineStr">
         <is>
-          <t>L554: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: TRAVELLERSâ€™</t>
+          <t>L1186: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | suspicious token(s): 60c (letter/digit mix) :: $selling heretotore at 60c a yard, for•</t>
         </is>
       </c>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L318: isolated marker/symbol line :: C</t>
+          <t>L308: isolated marker/symbol line :: &amp;</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
@@ -2019,7 +2059,11 @@
         </is>
       </c>
       <c r="R19" s="1" t="inlineStr"/>
-      <c r="S19" s="1" t="inlineStr"/>
+      <c r="S19" s="1" t="inlineStr">
+        <is>
+          <t>L1200: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text | suspicious token(s): 5c (letter/digit mix) :: • Ladies’ Vests at 5c each °</t>
+        </is>
+      </c>
       <c r="T19" s="1" t="inlineStr"/>
       <c r="U19" s="1" t="inlineStr"/>
       <c r="V19" s="1" t="inlineStr">
@@ -2046,24 +2090,20 @@
       </c>
       <c r="I20" s="1" t="inlineStr">
         <is>
-          <t>L1180: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | suspicious token(s): 25c (letter/digit mix) :: %25c a yard.â€¢</t>
-        </is>
-      </c>
-      <c r="J20" s="1" t="inlineStr">
-        <is>
-          <t>L909: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
-        </is>
-      </c>
+          <t>L1180: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | suspicious token(s): 25c (letter/digit mix) :: %25c a yard.•</t>
+        </is>
+      </c>
+      <c r="J20" s="1" t="inlineStr"/>
       <c r="K20" s="1" t="inlineStr">
         <is>
-          <t>L565: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: 36 James street south, over Molsonâ€™s Bank.</t>
+          <t>L1187: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text | suspicious token(s): 40c (letter/digit mix) :: • 40c a yard. .•</t>
         </is>
       </c>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L320: isolated marker/symbol line :: &amp;</t>
+          <t>L318: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
@@ -2078,7 +2118,11 @@
         </is>
       </c>
       <c r="R20" s="1" t="inlineStr"/>
-      <c r="S20" s="1" t="inlineStr"/>
+      <c r="S20" s="1" t="inlineStr">
+        <is>
+          <t>L1204: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • All kinds of Silk Lace Mitts, in•</t>
+        </is>
+      </c>
       <c r="T20" s="1" t="inlineStr"/>
       <c r="U20" s="1" t="inlineStr"/>
       <c r="V20" s="1" t="inlineStr">
@@ -2108,21 +2152,17 @@
           <t>L1182: line starts with punctuation glued to text | suspicious token(s): Dress2 (letter/digit mix) :: *All light shades in Woolen Dress2</t>
         </is>
       </c>
-      <c r="J21" s="1" t="inlineStr">
-        <is>
-          <t>L911: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
-        </is>
-      </c>
+      <c r="J21" s="1" t="inlineStr"/>
       <c r="K21" s="1" t="inlineStr">
         <is>
-          <t>L592: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: small amounts. No commission or agentâ€™s fees.</t>
+          <t>L1189: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: 1•The balance of a line we sold at $12</t>
         </is>
       </c>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L321: isolated marker/symbol line :: &amp;</t>
+          <t>L320: isolated marker/symbol line :: &amp;</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
@@ -2137,7 +2177,11 @@
         </is>
       </c>
       <c r="R21" s="1" t="inlineStr"/>
-      <c r="S21" s="1" t="inlineStr"/>
+      <c r="S21" s="1" t="inlineStr">
+        <is>
+          <t>L1208: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • at cost.</t>
+        </is>
+      </c>
       <c r="T21" s="1" t="inlineStr"/>
       <c r="U21" s="1" t="inlineStr"/>
       <c r="V21" s="1" t="inlineStr">
@@ -2164,24 +2208,20 @@
       </c>
       <c r="I22" s="1" t="inlineStr">
         <is>
-          <t>L1186: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | suspicious token(s): 60c (letter/digit mix) :: $selling heretotore at 60c a yard, forâ€¢</t>
-        </is>
-      </c>
-      <c r="J22" s="1" t="inlineStr">
-        <is>
-          <t>L912: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
-        </is>
-      </c>
+          <t>L1186: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | suspicious token(s): 60c (letter/digit mix) :: $selling heretotore at 60c a yard, for•</t>
+        </is>
+      </c>
+      <c r="J22" s="1" t="inlineStr"/>
       <c r="K22" s="1" t="inlineStr">
         <is>
-          <t>L623: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: repeated periods :: Accom.................â€¢</t>
+          <t>L1194: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text | suspicious token(s): 59c (letter/digit mix) :: • colors, at 59c each. •</t>
         </is>
       </c>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L333: isolated marker/symbol line :: G</t>
+          <t>L321: isolated marker/symbol line :: &amp;</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
@@ -2223,24 +2263,20 @@
       </c>
       <c r="I23" s="1" t="inlineStr">
         <is>
-          <t>L1187: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | suspicious token(s): 40c (letter/digit mix) :: â€¢ 40c a yard. .â€¢</t>
-        </is>
-      </c>
-      <c r="J23" s="1" t="inlineStr">
-        <is>
-          <t>L915: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
-        </is>
-      </c>
+          <t>L1187: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text | suspicious token(s): 40c (letter/digit mix) :: • 40c a yard. .•</t>
+        </is>
+      </c>
+      <c r="J23" s="1" t="inlineStr"/>
       <c r="K23" s="1" t="inlineStr">
         <is>
-          <t>L640: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: city property. No agentâ€™s fees or commission</t>
+          <t>L1196: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text | suspicious token(s): 75c (letter/digit mix) :: • Ladies’ Umbrellas at 75c each. *</t>
         </is>
       </c>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L341: isolated marker/symbol line :: S</t>
+          <t>L333: isolated marker/symbol line :: G</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
@@ -2282,24 +2318,20 @@
       </c>
       <c r="I24" s="1" t="inlineStr">
         <is>
-          <t>L1190: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE | punctuation artifact: double/multiple hyphen | suspicious token(s): 50c (letter/digit mix) :: 1â€˜a yard reduced for this sale to 50c a --</t>
-        </is>
-      </c>
-      <c r="J24" s="1" t="inlineStr">
-        <is>
-          <t>L916: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
-        </is>
-      </c>
+          <t>L1190: punctuation artifact: double/multiple hyphen | suspicious token(s): 50c (letter/digit mix) :: 1‘a yard reduced for this sale to 50c a --</t>
+        </is>
+      </c>
+      <c r="J24" s="1" t="inlineStr"/>
       <c r="K24" s="1" t="inlineStr">
         <is>
-          <t>L762: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 9a (letter/digit mix) :: street, Toronto. Office hour â€”9a. m. tolp.Â».,</t>
+          <t>L1198: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: • $1.50 each. •</t>
         </is>
       </c>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L342: isolated marker/symbol line :: S</t>
+          <t>L341: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
@@ -2337,24 +2369,20 @@
       </c>
       <c r="I25" s="1" t="inlineStr">
         <is>
-          <t>L1194: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | suspicious token(s): 59c (letter/digit mix) :: â€¢ colors, at 59c each. â€¢</t>
-        </is>
-      </c>
-      <c r="J25" s="1" t="inlineStr">
-        <is>
-          <t>L919: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
-        </is>
-      </c>
+          <t>L1194: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text | suspicious token(s): 59c (letter/digit mix) :: • colors, at 59c each. •</t>
+        </is>
+      </c>
+      <c r="J25" s="1" t="inlineStr"/>
       <c r="K25" s="1" t="inlineStr">
         <is>
-          <t>L763: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | abbreviation/spacing may be garbled :: 2 to 5 p.m. Dr. Batesâ€™ residence. No. 53 Augusta</t>
+          <t>L1200: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text | suspicious token(s): 5c (letter/digit mix) :: • Ladies’ Vests at 5c each °</t>
         </is>
       </c>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L352: isolated marker/symbol line :: &amp;</t>
+          <t>L342: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
@@ -2392,24 +2420,20 @@
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
-          <t>L1196: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): 75c (letter/digit mix) :: â€¢ Ladiesâ€™ Umbrellas at 75c each. *</t>
-        </is>
-      </c>
-      <c r="J26" s="1" t="inlineStr">
-        <is>
-          <t>L922: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
-        </is>
-      </c>
+          <t>L1196: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text | suspicious token(s): 75c (letter/digit mix) :: • Ladies’ Umbrellas at 75c each. *</t>
+        </is>
+      </c>
+      <c r="J26" s="1" t="inlineStr"/>
       <c r="K26" s="1" t="inlineStr">
         <is>
-          <t>L802: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Toronto Express........9.10â€”</t>
+          <t>L1203: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: %each.•</t>
         </is>
       </c>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L353: isolated marker/symbol line :: &amp;</t>
+          <t>L352: isolated marker/symbol line :: &amp;</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
@@ -2447,24 +2471,20 @@
       </c>
       <c r="I27" s="1" t="inlineStr">
         <is>
-          <t>L1200: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): 5c (letter/digit mix) :: â€¢ Ladiesâ€™ Vests at 5c each Â°</t>
-        </is>
-      </c>
-      <c r="J27" s="1" t="inlineStr">
-        <is>
-          <t>L923: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
-        </is>
-      </c>
+          <t>L1200: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text | suspicious token(s): 5c (letter/digit mix) :: • Ladies’ Vests at 5c each °</t>
+        </is>
+      </c>
+      <c r="J27" s="1" t="inlineStr"/>
       <c r="K27" s="1" t="inlineStr">
         <is>
-          <t>L881: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Nitrous oxide adminisâ€™ ered.</t>
+          <t>L1204: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • All kinds of Silk Lace Mitts, in•</t>
         </is>
       </c>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L356: isolated marker/symbol line :: S</t>
+          <t>L353: isolated marker/symbol line :: &amp;</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
@@ -2475,7 +2495,7 @@
       <c r="P27" s="1" t="inlineStr"/>
       <c r="Q27" s="1" t="inlineStr">
         <is>
-          <t>L802: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Toronto Express........9.10â€”</t>
+          <t>L802: punctuation artifact: repeated periods :: Toronto Express........9.10—</t>
         </is>
       </c>
       <c r="R27" s="1" t="inlineStr"/>
@@ -2505,21 +2525,17 @@
           <t>L1202: suspicious token(s): 30c (letter/digit mix), 19c (letter/digit mix) :: $ Ladies' Belts, worth 30c, for 19c $</t>
         </is>
       </c>
-      <c r="J28" s="1" t="inlineStr">
-        <is>
-          <t>L991: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Characteristics OF THE Studentsâ€™Mixture</t>
-        </is>
-      </c>
+      <c r="J28" s="1" t="inlineStr"/>
       <c r="K28" s="1" t="inlineStr">
         <is>
-          <t>L905: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: 'â€¢ Thank you," he responded, accepting</t>
+          <t>L1205: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: : • black, cream and fawn, at cost. 1:</t>
         </is>
       </c>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L363: isolated marker/symbol line :: .</t>
+          <t>L356: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
@@ -2560,21 +2576,17 @@
           <t>L1267: suspicious token(s): McKEAND (odd internal casing) :: GEORGE McKEAND,</t>
         </is>
       </c>
-      <c r="J29" s="1" t="inlineStr">
-        <is>
-          <t>L1243: stray/suspicious non-ASCII glyph(s): U+00AE REGISTERED SIGN | isolated marker/symbol line :: å®¶</t>
-        </is>
-      </c>
+      <c r="J29" s="1" t="inlineStr"/>
       <c r="K29" s="1" t="inlineStr">
         <is>
-          <t>L934: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: For Gentsâ€™ Summer Underwear, Socks,</t>
+          <t>L1207: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: %The balance of new Lace Curtains•</t>
         </is>
       </c>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L369: isolated marker/symbol line :: F</t>
+          <t>L363: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
@@ -2614,14 +2626,14 @@
       <c r="J30" s="1" t="inlineStr"/>
       <c r="K30" s="1" t="inlineStr">
         <is>
-          <t>L1010: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: flector.â€”House Furnishing Review.</t>
+          <t>L1208: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • at cost.</t>
         </is>
       </c>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L370: isolated marker/symbol line :: 4</t>
+          <t>L369: isolated marker/symbol line :: F</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
@@ -2661,14 +2673,14 @@
       <c r="J31" s="1" t="inlineStr"/>
       <c r="K31" s="1" t="inlineStr">
         <is>
-          <t>L1025: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: â€˜Runs on Sundays, but does not stop at inter-</t>
+          <t>L1226: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: = •</t>
         </is>
       </c>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L409: isolated marker/symbol line :: a</t>
+          <t>L370: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
@@ -2679,7 +2691,7 @@
       <c r="P31" s="1" t="inlineStr"/>
       <c r="Q31" s="1" t="inlineStr">
         <is>
-          <t>L1190: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE | punctuation artifact: double/multiple hyphen | suspicious token(s): 50c (letter/digit mix) :: 1â€˜a yard reduced for this sale to 50c a --</t>
+          <t>L1190: punctuation artifact: double/multiple hyphen | suspicious token(s): 50c (letter/digit mix) :: 1‘a yard reduced for this sale to 50c a --</t>
         </is>
       </c>
       <c r="R31" s="1" t="inlineStr"/>
@@ -2708,14 +2720,14 @@
       <c r="J32" s="1" t="inlineStr"/>
       <c r="K32" s="1" t="inlineStr">
         <is>
-          <t>L1074: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | abbreviation/spacing may be garbled :: From Dundas.â€”6.10, 8.00. 9.00, 10 15, 11.15 a.m.,</t>
+          <t>L1444: stray/suspicious non-ASCII glyph(s): U+25A0 BLACK SQUARE :: ed from life from people cured, free by mail.■</t>
         </is>
       </c>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L430: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
+          <t>L409: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr">
@@ -2753,16 +2765,12 @@
       </c>
       <c r="I33" s="1" t="inlineStr"/>
       <c r="J33" s="1" t="inlineStr"/>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>L1101: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: corner Mary. â€˜Phone 1,192.</t>
-        </is>
-      </c>
+      <c r="K33" s="1" t="inlineStr"/>
       <c r="L33" s="1" t="inlineStr"/>
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L495: isolated marker/symbol line :: a</t>
+          <t>L430: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr">
@@ -2800,16 +2808,12 @@
       </c>
       <c r="I34" s="1" t="inlineStr"/>
       <c r="J34" s="1" t="inlineStr"/>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>L1114: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Cayuga, Ont., June 28.â€”There was a</t>
-        </is>
-      </c>
+      <c r="K34" s="1" t="inlineStr"/>
       <c r="L34" s="1" t="inlineStr"/>
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L520: isolated marker/symbol line :: .</t>
+          <t>L472: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr">
@@ -2847,16 +2851,12 @@
       </c>
       <c r="I35" s="1" t="inlineStr"/>
       <c r="J35" s="1" t="inlineStr"/>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>L1123: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: was fractured. â€˜Wm. Stevenson,jr.,</t>
-        </is>
-      </c>
+      <c r="K35" s="1" t="inlineStr"/>
       <c r="L35" s="1" t="inlineStr"/>
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L657: isolated marker/symbol line :: A.</t>
+          <t>L495: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr">
@@ -2890,16 +2890,12 @@
       </c>
       <c r="I36" s="1" t="inlineStr"/>
       <c r="J36" s="1" t="inlineStr"/>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>L1137: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Fletcherâ€™s planing mills, Yonge street,</t>
-        </is>
-      </c>
+      <c r="K36" s="1" t="inlineStr"/>
       <c r="L36" s="1" t="inlineStr"/>
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L659: isolated marker/symbol line :: H.</t>
+          <t>L520: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr">
@@ -2933,16 +2929,12 @@
       </c>
       <c r="I37" s="1" t="inlineStr"/>
       <c r="J37" s="1" t="inlineStr"/>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>L1148: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: where the injured arm â€žas amputated.</t>
-        </is>
-      </c>
+      <c r="K37" s="1" t="inlineStr"/>
       <c r="L37" s="1" t="inlineStr"/>
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L685: symbol-only separator/garbage line :: $100, 000</t>
+          <t>L627: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="O37" s="1" t="inlineStr">
@@ -2976,16 +2968,12 @@
       </c>
       <c r="I38" s="1" t="inlineStr"/>
       <c r="J38" s="1" t="inlineStr"/>
-      <c r="K38" s="1" t="inlineStr">
-        <is>
-          <t>L1171: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ materials, we will offer Dress Goodsâ€¢</t>
-        </is>
-      </c>
+      <c r="K38" s="1" t="inlineStr"/>
       <c r="L38" s="1" t="inlineStr"/>
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L702: symbol-only separator/garbage line :: $50, 000</t>
+          <t>L657: isolated marker/symbol line :: A.</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr">
@@ -3019,16 +3007,12 @@
       </c>
       <c r="I39" s="1" t="inlineStr"/>
       <c r="J39" s="1" t="inlineStr"/>
-      <c r="K39" s="1" t="inlineStr">
-        <is>
-          <t>L1172: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢â–ºat the cost price and in some instances 1,</t>
-        </is>
-      </c>
+      <c r="K39" s="1" t="inlineStr"/>
       <c r="L39" s="1" t="inlineStr"/>
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L703: isolated marker/symbol line :: X</t>
+          <t>L659: isolated marker/symbol line :: H.</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr">
@@ -3062,16 +3046,12 @@
       </c>
       <c r="I40" s="1" t="inlineStr"/>
       <c r="J40" s="1" t="inlineStr"/>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>L1173: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: $at even less than what we paid forâ€¢</t>
-        </is>
-      </c>
+      <c r="K40" s="1" t="inlineStr"/>
       <c r="L40" s="1" t="inlineStr"/>
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L711: isolated marker/symbol line :: D</t>
+          <t>L685: symbol-only separator/garbage line :: $100, 000</t>
         </is>
       </c>
       <c r="O40" s="1" t="inlineStr">
@@ -3105,16 +3085,12 @@
       </c>
       <c r="I41" s="1" t="inlineStr"/>
       <c r="J41" s="1" t="inlineStr"/>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>L1174: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢them.â€¢</t>
-        </is>
-      </c>
+      <c r="K41" s="1" t="inlineStr"/>
       <c r="L41" s="1" t="inlineStr"/>
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L720: isolated marker/symbol line :: T</t>
+          <t>L702: symbol-only separator/garbage line :: $50, 000</t>
         </is>
       </c>
       <c r="O41" s="1" t="inlineStr">
@@ -3148,21 +3124,17 @@
       </c>
       <c r="I42" s="1" t="inlineStr"/>
       <c r="J42" s="1" t="inlineStr"/>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t>L1175: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | suspicious token(s): 25c (letter/digit mix), 28c (letter/digit mix), 30c (letter/digit mix) :: â€¢The balance of the 25c, 28c and 30c$</t>
-        </is>
-      </c>
+      <c r="K42" s="1" t="inlineStr"/>
       <c r="L42" s="1" t="inlineStr"/>
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L729: isolated marker/symbol line :: D.</t>
+          <t>L703: isolated marker/symbol line :: X</t>
         </is>
       </c>
       <c r="O42" s="1" t="inlineStr">
         <is>
-          <t>L1300: isolated marker/symbol line :: "</t>
+          <t>L1226: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: = •</t>
         </is>
       </c>
       <c r="P42" s="1" t="inlineStr"/>
@@ -3187,21 +3159,17 @@
       <c r="H43" s="1" t="inlineStr"/>
       <c r="I43" s="1" t="inlineStr"/>
       <c r="J43" s="1" t="inlineStr"/>
-      <c r="K43" s="1" t="inlineStr">
-        <is>
-          <t>L1177: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | suspicious token(s): 30c (letter/digit mix) :: $All that's left of the 30c All-woolâ€¢</t>
-        </is>
-      </c>
+      <c r="K43" s="1" t="inlineStr"/>
       <c r="L43" s="1" t="inlineStr"/>
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L734: isolated marker/symbol line :: R.</t>
+          <t>L704: stray/suspicious non-ASCII glyph(s): U+4EA7 CJK UNIFIED IDEOGRAPH-4EA7 | isolated marker/symbol line :: 产</t>
         </is>
       </c>
       <c r="O43" s="1" t="inlineStr">
         <is>
-          <t>L1364: symbol-only separator/garbage line :: *****************-</t>
+          <t>L1300: isolated marker/symbol line :: "</t>
         </is>
       </c>
       <c r="P43" s="1" t="inlineStr"/>
@@ -3226,21 +3194,17 @@
       <c r="H44" s="1" t="inlineStr"/>
       <c r="I44" s="1" t="inlineStr"/>
       <c r="J44" s="1" t="inlineStr"/>
-      <c r="K44" s="1" t="inlineStr">
-        <is>
-          <t>L1178: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ Delaines at 19%ca yard.$</t>
-        </is>
-      </c>
+      <c r="K44" s="1" t="inlineStr"/>
       <c r="L44" s="1" t="inlineStr"/>
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L739: isolated marker/symbol line :: D</t>
+          <t>L711: isolated marker/symbol line :: D</t>
         </is>
       </c>
       <c r="O44" s="1" t="inlineStr">
         <is>
-          <t>L1368: symbol-only separator/garbage line :: ***************</t>
+          <t>L1364: symbol-only separator/garbage line :: *****************-</t>
         </is>
       </c>
       <c r="P44" s="1" t="inlineStr"/>
@@ -3265,21 +3229,17 @@
       <c r="H45" s="1" t="inlineStr"/>
       <c r="I45" s="1" t="inlineStr"/>
       <c r="J45" s="1" t="inlineStr"/>
-      <c r="K45" s="1" t="inlineStr">
-        <is>
-          <t>L1180: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | suspicious token(s): 25c (letter/digit mix) :: %25c a yard.â€¢</t>
-        </is>
-      </c>
+      <c r="K45" s="1" t="inlineStr"/>
       <c r="L45" s="1" t="inlineStr"/>
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L746: isolated marker/symbol line :: E.</t>
+          <t>L720: isolated marker/symbol line :: T</t>
         </is>
       </c>
       <c r="O45" s="1" t="inlineStr">
         <is>
-          <t>L1374: isolated marker/symbol line :: 0</t>
+          <t>L1368: symbol-only separator/garbage line :: ***************</t>
         </is>
       </c>
       <c r="P45" s="1" t="inlineStr"/>
@@ -3304,21 +3264,17 @@
       <c r="H46" s="1" t="inlineStr"/>
       <c r="I46" s="1" t="inlineStr"/>
       <c r="J46" s="1" t="inlineStr"/>
-      <c r="K46" s="1" t="inlineStr">
-        <is>
-          <t>L1181: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ All Spotted White Muslins at cost.X</t>
-        </is>
-      </c>
+      <c r="K46" s="1" t="inlineStr"/>
       <c r="L46" s="1" t="inlineStr"/>
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L748: isolated marker/symbol line :: D.&amp;</t>
+          <t>L729: isolated marker/symbol line :: D.</t>
         </is>
       </c>
       <c r="O46" s="1" t="inlineStr">
         <is>
-          <t>L1439: isolated marker/symbol line :: *</t>
+          <t>L1374: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P46" s="1" t="inlineStr"/>
@@ -3343,21 +3299,17 @@
       <c r="H47" s="1" t="inlineStr"/>
       <c r="I47" s="1" t="inlineStr"/>
       <c r="J47" s="1" t="inlineStr"/>
-      <c r="K47" s="1" t="inlineStr">
-        <is>
-          <t>L1183: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: $Materials at cost and under.â€¢</t>
-        </is>
-      </c>
+      <c r="K47" s="1" t="inlineStr"/>
       <c r="L47" s="1" t="inlineStr"/>
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L753: isolated marker/symbol line :: D</t>
+          <t>L734: isolated marker/symbol line :: R.</t>
         </is>
       </c>
       <c r="O47" s="1" t="inlineStr">
         <is>
-          <t>L1450: isolated marker/symbol line :: :</t>
+          <t>L1439: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="P47" s="1" t="inlineStr"/>
@@ -3382,21 +3334,17 @@
       <c r="H48" s="1" t="inlineStr"/>
       <c r="I48" s="1" t="inlineStr"/>
       <c r="J48" s="1" t="inlineStr"/>
-      <c r="K48" s="1" t="inlineStr">
-        <is>
-          <t>L1184: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢The choice of the balance of ourâ€¢</t>
-        </is>
-      </c>
+      <c r="K48" s="1" t="inlineStr"/>
       <c r="L48" s="1" t="inlineStr"/>
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L757: isolated marker/symbol line :: F.</t>
+          <t>L739: isolated marker/symbol line :: D</t>
         </is>
       </c>
       <c r="O48" s="1" t="inlineStr">
         <is>
-          <t>L1467: symbol-only separator/garbage line :: *********************</t>
+          <t>L1450: isolated marker/symbol line :: :</t>
         </is>
       </c>
       <c r="P48" s="1" t="inlineStr"/>
@@ -3421,21 +3369,17 @@
       <c r="H49" s="1" t="inlineStr"/>
       <c r="I49" s="1" t="inlineStr"/>
       <c r="J49" s="1" t="inlineStr"/>
-      <c r="K49" s="1" t="inlineStr">
-        <is>
-          <t>L1185: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: 1â€¢ latest and very stylish Dress Materials,$</t>
-        </is>
-      </c>
+      <c r="K49" s="1" t="inlineStr"/>
       <c r="L49" s="1" t="inlineStr"/>
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>L776: symbol-only separator/garbage line :: 9.05</t>
+          <t>L746: isolated marker/symbol line :: E.</t>
         </is>
       </c>
       <c r="O49" s="1" t="inlineStr">
         <is>
-          <t>L1477: isolated marker/symbol line :: -</t>
+          <t>L1467: symbol-only separator/garbage line :: *********************</t>
         </is>
       </c>
       <c r="P49" s="1" t="inlineStr"/>
@@ -3460,19 +3404,19 @@
       <c r="H50" s="1" t="inlineStr"/>
       <c r="I50" s="1" t="inlineStr"/>
       <c r="J50" s="1" t="inlineStr"/>
-      <c r="K50" s="1" t="inlineStr">
-        <is>
-          <t>L1186: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | suspicious token(s): 60c (letter/digit mix) :: $selling heretotore at 60c a yard, forâ€¢</t>
-        </is>
-      </c>
+      <c r="K50" s="1" t="inlineStr"/>
       <c r="L50" s="1" t="inlineStr"/>
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr">
         <is>
-          <t>L777: symbol-only separator/garbage line :: 9.15</t>
-        </is>
-      </c>
-      <c r="O50" s="1" t="inlineStr"/>
+          <t>L748: isolated marker/symbol line :: D.&amp;</t>
+        </is>
+      </c>
+      <c r="O50" s="1" t="inlineStr">
+        <is>
+          <t>L1477: isolated marker/symbol line :: -</t>
+        </is>
+      </c>
       <c r="P50" s="1" t="inlineStr"/>
       <c r="Q50" s="1" t="inlineStr"/>
       <c r="R50" s="1" t="inlineStr"/>
@@ -3495,16 +3439,12 @@
       <c r="H51" s="1" t="inlineStr"/>
       <c r="I51" s="1" t="inlineStr"/>
       <c r="J51" s="1" t="inlineStr"/>
-      <c r="K51" s="1" t="inlineStr">
-        <is>
-          <t>L1187: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | suspicious token(s): 40c (letter/digit mix) :: â€¢ 40c a yard. .â€¢</t>
-        </is>
-      </c>
+      <c r="K51" s="1" t="inlineStr"/>
       <c r="L51" s="1" t="inlineStr"/>
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr">
         <is>
-          <t>L785: symbol-only separator/garbage line :: 5.35</t>
+          <t>L753: isolated marker/symbol line :: D</t>
         </is>
       </c>
       <c r="O51" s="1" t="inlineStr"/>
@@ -3530,16 +3470,12 @@
       <c r="H52" s="1" t="inlineStr"/>
       <c r="I52" s="1" t="inlineStr"/>
       <c r="J52" s="1" t="inlineStr"/>
-      <c r="K52" s="1" t="inlineStr">
-        <is>
-          <t>L1189: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: 1â€¢The balance of a line we sold at $12</t>
-        </is>
-      </c>
+      <c r="K52" s="1" t="inlineStr"/>
       <c r="L52" s="1" t="inlineStr"/>
       <c r="M52" s="1" t="inlineStr"/>
       <c r="N52" s="1" t="inlineStr">
         <is>
-          <t>L786: symbol-only separator/garbage line :: 5.40</t>
+          <t>L757: isolated marker/symbol line :: F.</t>
         </is>
       </c>
       <c r="O52" s="1" t="inlineStr"/>
@@ -3565,16 +3501,12 @@
       <c r="H53" s="1" t="inlineStr"/>
       <c r="I53" s="1" t="inlineStr"/>
       <c r="J53" s="1" t="inlineStr"/>
-      <c r="K53" s="1" t="inlineStr">
-        <is>
-          <t>L1190: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE | punctuation artifact: double/multiple hyphen | suspicious token(s): 50c (letter/digit mix) :: 1â€˜a yard reduced for this sale to 50c a --</t>
-        </is>
-      </c>
+      <c r="K53" s="1" t="inlineStr"/>
       <c r="L53" s="1" t="inlineStr"/>
       <c r="M53" s="1" t="inlineStr"/>
       <c r="N53" s="1" t="inlineStr">
         <is>
-          <t>L789: symbol-only separator/garbage line :: 6.38</t>
+          <t>L772: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O53" s="1" t="inlineStr"/>
@@ -3600,16 +3532,12 @@
       <c r="H54" s="1" t="inlineStr"/>
       <c r="I54" s="1" t="inlineStr"/>
       <c r="J54" s="1" t="inlineStr"/>
-      <c r="K54" s="1" t="inlineStr">
-        <is>
-          <t>L1194: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | suspicious token(s): 59c (letter/digit mix) :: â€¢ colors, at 59c each. â€¢</t>
-        </is>
-      </c>
+      <c r="K54" s="1" t="inlineStr"/>
       <c r="L54" s="1" t="inlineStr"/>
       <c r="M54" s="1" t="inlineStr"/>
       <c r="N54" s="1" t="inlineStr">
         <is>
-          <t>L790: symbol-only separator/garbage line :: 6.47</t>
+          <t>L776: symbol-only separator/garbage line :: 9.05</t>
         </is>
       </c>
       <c r="O54" s="1" t="inlineStr"/>
@@ -3635,16 +3563,12 @@
       <c r="H55" s="1" t="inlineStr"/>
       <c r="I55" s="1" t="inlineStr"/>
       <c r="J55" s="1" t="inlineStr"/>
-      <c r="K55" s="1" t="inlineStr">
-        <is>
-          <t>L1196: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): 75c (letter/digit mix) :: â€¢ Ladiesâ€™ Umbrellas at 75c each. *</t>
-        </is>
-      </c>
+      <c r="K55" s="1" t="inlineStr"/>
       <c r="L55" s="1" t="inlineStr"/>
       <c r="M55" s="1" t="inlineStr"/>
       <c r="N55" s="1" t="inlineStr">
         <is>
-          <t>L792: symbol-only separator/garbage line :: 8.00</t>
+          <t>L777: symbol-only separator/garbage line :: 9.15</t>
         </is>
       </c>
       <c r="O55" s="1" t="inlineStr"/>
@@ -3670,16 +3594,12 @@
       <c r="H56" s="1" t="inlineStr"/>
       <c r="I56" s="1" t="inlineStr"/>
       <c r="J56" s="1" t="inlineStr"/>
-      <c r="K56" s="1" t="inlineStr">
-        <is>
-          <t>L1198: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ $1.50 each. â€¢</t>
-        </is>
-      </c>
+      <c r="K56" s="1" t="inlineStr"/>
       <c r="L56" s="1" t="inlineStr"/>
       <c r="M56" s="1" t="inlineStr"/>
       <c r="N56" s="1" t="inlineStr">
         <is>
-          <t>L793: symbol-only separator/garbage line :: 8.20</t>
+          <t>L785: symbol-only separator/garbage line :: 5.35</t>
         </is>
       </c>
       <c r="O56" s="1" t="inlineStr"/>
@@ -3705,16 +3625,12 @@
       <c r="H57" s="1" t="inlineStr"/>
       <c r="I57" s="1" t="inlineStr"/>
       <c r="J57" s="1" t="inlineStr"/>
-      <c r="K57" s="1" t="inlineStr">
-        <is>
-          <t>L1200: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): 5c (letter/digit mix) :: â€¢ Ladiesâ€™ Vests at 5c each Â°</t>
-        </is>
-      </c>
+      <c r="K57" s="1" t="inlineStr"/>
       <c r="L57" s="1" t="inlineStr"/>
       <c r="M57" s="1" t="inlineStr"/>
       <c r="N57" s="1" t="inlineStr">
         <is>
-          <t>L801: symbol-only separator/garbage line :: 7.10</t>
+          <t>L786: symbol-only separator/garbage line :: 5.40</t>
         </is>
       </c>
       <c r="O57" s="1" t="inlineStr"/>
@@ -3740,16 +3656,12 @@
       <c r="H58" s="1" t="inlineStr"/>
       <c r="I58" s="1" t="inlineStr"/>
       <c r="J58" s="1" t="inlineStr"/>
-      <c r="K58" s="1" t="inlineStr">
-        <is>
-          <t>L1203: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: %each.â€¢</t>
-        </is>
-      </c>
+      <c r="K58" s="1" t="inlineStr"/>
       <c r="L58" s="1" t="inlineStr"/>
       <c r="M58" s="1" t="inlineStr"/>
       <c r="N58" s="1" t="inlineStr">
         <is>
-          <t>L804: symbol-only separator/garbage line :: 8.35</t>
+          <t>L789: symbol-only separator/garbage line :: 6.38</t>
         </is>
       </c>
       <c r="O58" s="1" t="inlineStr"/>
@@ -3775,16 +3687,12 @@
       <c r="H59" s="1" t="inlineStr"/>
       <c r="I59" s="1" t="inlineStr"/>
       <c r="J59" s="1" t="inlineStr"/>
-      <c r="K59" s="1" t="inlineStr">
-        <is>
-          <t>L1204: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ All kinds of Silk Lace Mitts, inâ€¢</t>
-        </is>
-      </c>
+      <c r="K59" s="1" t="inlineStr"/>
       <c r="L59" s="1" t="inlineStr"/>
       <c r="M59" s="1" t="inlineStr"/>
       <c r="N59" s="1" t="inlineStr">
         <is>
-          <t>L805: symbol-only separator/garbage line :: 8.40</t>
+          <t>L790: symbol-only separator/garbage line :: 6.47</t>
         </is>
       </c>
       <c r="O59" s="1" t="inlineStr"/>
@@ -3810,16 +3718,12 @@
       <c r="H60" s="1" t="inlineStr"/>
       <c r="I60" s="1" t="inlineStr"/>
       <c r="J60" s="1" t="inlineStr"/>
-      <c r="K60" s="1" t="inlineStr">
-        <is>
-          <t>L1205: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: : â€¢ black, cream and fawn, at cost. 1:</t>
-        </is>
-      </c>
+      <c r="K60" s="1" t="inlineStr"/>
       <c r="L60" s="1" t="inlineStr"/>
       <c r="M60" s="1" t="inlineStr"/>
       <c r="N60" s="1" t="inlineStr">
         <is>
-          <t>L808: symbol-only separator/garbage line :: 9.05</t>
+          <t>L792: symbol-only separator/garbage line :: 8.00</t>
         </is>
       </c>
       <c r="O60" s="1" t="inlineStr"/>
@@ -3845,16 +3749,12 @@
       <c r="H61" s="1" t="inlineStr"/>
       <c r="I61" s="1" t="inlineStr"/>
       <c r="J61" s="1" t="inlineStr"/>
-      <c r="K61" s="1" t="inlineStr">
-        <is>
-          <t>L1207: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: %The balance of new Lace Curtainsâ€¢</t>
-        </is>
-      </c>
+      <c r="K61" s="1" t="inlineStr"/>
       <c r="L61" s="1" t="inlineStr"/>
       <c r="M61" s="1" t="inlineStr"/>
       <c r="N61" s="1" t="inlineStr">
         <is>
-          <t>L809: symbol-only separator/garbage line :: 9.05</t>
+          <t>L793: symbol-only separator/garbage line :: 8.20</t>
         </is>
       </c>
       <c r="O61" s="1" t="inlineStr"/>
@@ -3880,16 +3780,12 @@
       <c r="H62" s="1" t="inlineStr"/>
       <c r="I62" s="1" t="inlineStr"/>
       <c r="J62" s="1" t="inlineStr"/>
-      <c r="K62" s="1" t="inlineStr">
-        <is>
-          <t>L1208: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ at cost.</t>
-        </is>
-      </c>
+      <c r="K62" s="1" t="inlineStr"/>
       <c r="L62" s="1" t="inlineStr"/>
       <c r="M62" s="1" t="inlineStr"/>
       <c r="N62" s="1" t="inlineStr">
         <is>
-          <t>L812: symbol-only separator/garbage line :: 9.53</t>
+          <t>L801: symbol-only separator/garbage line :: 7.10</t>
         </is>
       </c>
       <c r="O62" s="1" t="inlineStr"/>
@@ -3915,16 +3811,12 @@
       <c r="H63" s="1" t="inlineStr"/>
       <c r="I63" s="1" t="inlineStr"/>
       <c r="J63" s="1" t="inlineStr"/>
-      <c r="K63" s="1" t="inlineStr">
-        <is>
-          <t>L1226: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: = â€¢</t>
-        </is>
-      </c>
+      <c r="K63" s="1" t="inlineStr"/>
       <c r="L63" s="1" t="inlineStr"/>
       <c r="M63" s="1" t="inlineStr"/>
       <c r="N63" s="1" t="inlineStr">
         <is>
-          <t>L813: symbol-only separator/garbage line :: 10.00</t>
+          <t>L804: symbol-only separator/garbage line :: 8.35</t>
         </is>
       </c>
       <c r="O63" s="1" t="inlineStr"/>
@@ -3950,16 +3842,12 @@
       <c r="H64" s="1" t="inlineStr"/>
       <c r="I64" s="1" t="inlineStr"/>
       <c r="J64" s="1" t="inlineStr"/>
-      <c r="K64" s="1" t="inlineStr">
-        <is>
-          <t>L1305: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: tonic and blood purifier like Hoodâ€™s Sar-</t>
-        </is>
-      </c>
+      <c r="K64" s="1" t="inlineStr"/>
       <c r="L64" s="1" t="inlineStr"/>
       <c r="M64" s="1" t="inlineStr"/>
       <c r="N64" s="1" t="inlineStr">
         <is>
-          <t>L815: symbol-only separator/garbage line :: 8.25</t>
+          <t>L805: symbol-only separator/garbage line :: 8.40</t>
         </is>
       </c>
       <c r="O64" s="1" t="inlineStr"/>
@@ -3985,16 +3873,12 @@
       <c r="H65" s="1" t="inlineStr"/>
       <c r="I65" s="1" t="inlineStr"/>
       <c r="J65" s="1" t="inlineStr"/>
-      <c r="K65" s="1" t="inlineStr">
-        <is>
-          <t>L1335: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: to taste : stir till it boilsâ€”it should not</t>
-        </is>
-      </c>
+      <c r="K65" s="1" t="inlineStr"/>
       <c r="L65" s="1" t="inlineStr"/>
       <c r="M65" s="1" t="inlineStr"/>
       <c r="N65" s="1" t="inlineStr">
         <is>
-          <t>L816: symbol-only separator/garbage line :: 9.20</t>
+          <t>L808: symbol-only separator/garbage line :: 9.05</t>
         </is>
       </c>
       <c r="O65" s="1" t="inlineStr"/>
@@ -4020,16 +3904,12 @@
       <c r="H66" s="1" t="inlineStr"/>
       <c r="I66" s="1" t="inlineStr"/>
       <c r="J66" s="1" t="inlineStr"/>
-      <c r="K66" s="1" t="inlineStr">
-        <is>
-          <t>L1359: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Trebleâ€™s, corner King and James streets.</t>
-        </is>
-      </c>
+      <c r="K66" s="1" t="inlineStr"/>
       <c r="L66" s="1" t="inlineStr"/>
       <c r="M66" s="1" t="inlineStr"/>
       <c r="N66" s="1" t="inlineStr">
         <is>
-          <t>L818: isolated marker/symbol line :: .</t>
+          <t>L809: symbol-only separator/garbage line :: 9.05</t>
         </is>
       </c>
       <c r="O66" s="1" t="inlineStr"/>
@@ -4055,16 +3935,12 @@
       <c r="H67" s="1" t="inlineStr"/>
       <c r="I67" s="1" t="inlineStr"/>
       <c r="J67" s="1" t="inlineStr"/>
-      <c r="K67" s="1" t="inlineStr">
-        <is>
-          <t>L1390: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Lew isâ€™ Cottee Tavern, King St. Station.</t>
-        </is>
-      </c>
+      <c r="K67" s="1" t="inlineStr"/>
       <c r="L67" s="1" t="inlineStr"/>
       <c r="M67" s="1" t="inlineStr"/>
       <c r="N67" s="1" t="inlineStr">
         <is>
-          <t>L819: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 11.05</t>
+          <t>L812: symbol-only separator/garbage line :: 9.53</t>
         </is>
       </c>
       <c r="O67" s="1" t="inlineStr"/>
@@ -4090,16 +3966,12 @@
       <c r="H68" s="1" t="inlineStr"/>
       <c r="I68" s="1" t="inlineStr"/>
       <c r="J68" s="1" t="inlineStr"/>
-      <c r="K68" s="1" t="inlineStr">
-        <is>
-          <t>L1428: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: DO, Toronto, On*. Write for in " Set Sold iâ€”</t>
-        </is>
-      </c>
+      <c r="K68" s="1" t="inlineStr"/>
       <c r="L68" s="1" t="inlineStr"/>
       <c r="M68" s="1" t="inlineStr"/>
       <c r="N68" s="1" t="inlineStr">
         <is>
-          <t>L827: symbol-only separator/garbage line :: 6.40</t>
+          <t>L813: symbol-only separator/garbage line :: 10.00</t>
         </is>
       </c>
       <c r="O68" s="1" t="inlineStr"/>
@@ -4130,7 +4002,7 @@
       <c r="M69" s="1" t="inlineStr"/>
       <c r="N69" s="1" t="inlineStr">
         <is>
-          <t>L828: symbol-only separator/garbage line :: 6.55</t>
+          <t>L815: symbol-only separator/garbage line :: 8.25</t>
         </is>
       </c>
       <c r="O69" s="1" t="inlineStr"/>
@@ -4161,7 +4033,7 @@
       <c r="M70" s="1" t="inlineStr"/>
       <c r="N70" s="1" t="inlineStr">
         <is>
-          <t>L830: symbol-only separator/garbage line :: 9.10</t>
+          <t>L816: symbol-only separator/garbage line :: 9.20</t>
         </is>
       </c>
       <c r="O70" s="1" t="inlineStr"/>
@@ -4192,7 +4064,7 @@
       <c r="M71" s="1" t="inlineStr"/>
       <c r="N71" s="1" t="inlineStr">
         <is>
-          <t>L841: isolated marker/symbol line :: .</t>
+          <t>L818: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O71" s="1" t="inlineStr"/>
@@ -4223,7 +4095,7 @@
       <c r="M72" s="1" t="inlineStr"/>
       <c r="N72" s="1" t="inlineStr">
         <is>
-          <t>L842: symbol-only separator/garbage line :: 10.25</t>
+          <t>L819: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 11.05</t>
         </is>
       </c>
       <c r="O72" s="1" t="inlineStr"/>
@@ -4254,7 +4126,7 @@
       <c r="M73" s="1" t="inlineStr"/>
       <c r="N73" s="1" t="inlineStr">
         <is>
-          <t>L844: isolated marker/symbol line :: 66</t>
+          <t>L827: symbol-only separator/garbage line :: 6.40</t>
         </is>
       </c>
       <c r="O73" s="1" t="inlineStr"/>
@@ -4285,7 +4157,7 @@
       <c r="M74" s="1" t="inlineStr"/>
       <c r="N74" s="1" t="inlineStr">
         <is>
-          <t>L846: symbol-only separator/garbage line :: 11.10</t>
+          <t>L828: symbol-only separator/garbage line :: 6.55</t>
         </is>
       </c>
       <c r="O74" s="1" t="inlineStr"/>
@@ -4316,7 +4188,7 @@
       <c r="M75" s="1" t="inlineStr"/>
       <c r="N75" s="1" t="inlineStr">
         <is>
-          <t>L847: isolated marker/symbol line :: .</t>
+          <t>L830: symbol-only separator/garbage line :: 9.10</t>
         </is>
       </c>
       <c r="O75" s="1" t="inlineStr"/>
@@ -4347,7 +4219,7 @@
       <c r="M76" s="1" t="inlineStr"/>
       <c r="N76" s="1" t="inlineStr">
         <is>
-          <t>L852: symbol-only separator/garbage line :: 1.50</t>
+          <t>L839: symbol-only separator/garbage line :: †9.20</t>
         </is>
       </c>
       <c r="O76" s="1" t="inlineStr"/>
@@ -4378,7 +4250,7 @@
       <c r="M77" s="1" t="inlineStr"/>
       <c r="N77" s="1" t="inlineStr">
         <is>
-          <t>L854: isolated marker/symbol line :: .</t>
+          <t>L840: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="O77" s="1" t="inlineStr"/>
@@ -4409,7 +4281,7 @@
       <c r="M78" s="1" t="inlineStr"/>
       <c r="N78" s="1" t="inlineStr">
         <is>
-          <t>L856: symbol-only separator/garbage line :: 4.10</t>
+          <t>L841: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O78" s="1" t="inlineStr"/>
@@ -4440,7 +4312,7 @@
       <c r="M79" s="1" t="inlineStr"/>
       <c r="N79" s="1" t="inlineStr">
         <is>
-          <t>L857: isolated marker/symbol line :: :</t>
+          <t>L842: symbol-only separator/garbage line :: 10.25</t>
         </is>
       </c>
       <c r="O79" s="1" t="inlineStr"/>
@@ -4471,7 +4343,7 @@
       <c r="M80" s="1" t="inlineStr"/>
       <c r="N80" s="1" t="inlineStr">
         <is>
-          <t>L858: isolated marker/symbol line :: .</t>
+          <t>L843: isolated marker/symbol line :: “</t>
         </is>
       </c>
       <c r="O80" s="1" t="inlineStr"/>
@@ -4502,7 +4374,7 @@
       <c r="M81" s="1" t="inlineStr"/>
       <c r="N81" s="1" t="inlineStr">
         <is>
-          <t>L859: symbol-only separator/garbage line :: 5.25</t>
+          <t>L844: isolated marker/symbol line :: 66</t>
         </is>
       </c>
       <c r="O81" s="1" t="inlineStr"/>
@@ -4533,7 +4405,7 @@
       <c r="M82" s="1" t="inlineStr"/>
       <c r="N82" s="1" t="inlineStr">
         <is>
-          <t>L863: symbol-only separator/garbage line :: 5.40</t>
+          <t>L846: symbol-only separator/garbage line :: 11.10</t>
         </is>
       </c>
       <c r="O82" s="1" t="inlineStr"/>
@@ -4564,7 +4436,7 @@
       <c r="M83" s="1" t="inlineStr"/>
       <c r="N83" s="1" t="inlineStr">
         <is>
-          <t>L865: isolated marker/symbol line :: .</t>
+          <t>L847: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O83" s="1" t="inlineStr"/>
@@ -4595,7 +4467,7 @@
       <c r="M84" s="1" t="inlineStr"/>
       <c r="N84" s="1" t="inlineStr">
         <is>
-          <t>L866: symbol-only separator/garbage line :: 7.05</t>
+          <t>L848: isolated marker/symbol line :: “</t>
         </is>
       </c>
       <c r="O84" s="1" t="inlineStr"/>
@@ -4626,7 +4498,7 @@
       <c r="M85" s="1" t="inlineStr"/>
       <c r="N85" s="1" t="inlineStr">
         <is>
-          <t>L870: symbol-only separator/garbage line :: 6.55</t>
+          <t>L852: symbol-only separator/garbage line :: 1.50</t>
         </is>
       </c>
       <c r="O85" s="1" t="inlineStr"/>
@@ -4657,7 +4529,7 @@
       <c r="M86" s="1" t="inlineStr"/>
       <c r="N86" s="1" t="inlineStr">
         <is>
-          <t>L873: symbol-only separator/garbage line :: 8.10</t>
+          <t>L853: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="O86" s="1" t="inlineStr"/>
@@ -4688,7 +4560,7 @@
       <c r="M87" s="1" t="inlineStr"/>
       <c r="N87" s="1" t="inlineStr">
         <is>
-          <t>L875: isolated marker/symbol line :: "</t>
+          <t>L854: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O87" s="1" t="inlineStr"/>
@@ -4719,7 +4591,7 @@
       <c r="M88" s="1" t="inlineStr"/>
       <c r="N88" s="1" t="inlineStr">
         <is>
-          <t>L877: symbol-only separator/garbage line :: 9.20</t>
+          <t>L856: symbol-only separator/garbage line :: 4.10</t>
         </is>
       </c>
       <c r="O88" s="1" t="inlineStr"/>
@@ -4750,7 +4622,7 @@
       <c r="M89" s="1" t="inlineStr"/>
       <c r="N89" s="1" t="inlineStr">
         <is>
-          <t>L880: symbol-only separator/garbage line :: 10.30</t>
+          <t>L857: isolated marker/symbol line :: :</t>
         </is>
       </c>
       <c r="O89" s="1" t="inlineStr"/>
@@ -4781,7 +4653,7 @@
       <c r="M90" s="1" t="inlineStr"/>
       <c r="N90" s="1" t="inlineStr">
         <is>
-          <t>L892: symbol-only separator/garbage line :: 8.45</t>
+          <t>L858: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O90" s="1" t="inlineStr"/>
@@ -4812,7 +4684,7 @@
       <c r="M91" s="1" t="inlineStr"/>
       <c r="N91" s="1" t="inlineStr">
         <is>
-          <t>L893: isolated marker/symbol line :: 6</t>
+          <t>L859: symbol-only separator/garbage line :: 5.25</t>
         </is>
       </c>
       <c r="O91" s="1" t="inlineStr"/>
@@ -4843,7 +4715,7 @@
       <c r="M92" s="1" t="inlineStr"/>
       <c r="N92" s="1" t="inlineStr">
         <is>
-          <t>L894: symbol-only separator/garbage line :: 9.65</t>
+          <t>L860: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="O92" s="1" t="inlineStr"/>
@@ -4874,7 +4746,7 @@
       <c r="M93" s="1" t="inlineStr"/>
       <c r="N93" s="1" t="inlineStr">
         <is>
-          <t>L900: symbol-only separator/garbage line :: 2.50</t>
+          <t>L861: isolated marker/symbol line :: “</t>
         </is>
       </c>
       <c r="O93" s="1" t="inlineStr"/>
@@ -4905,7 +4777,7 @@
       <c r="M94" s="1" t="inlineStr"/>
       <c r="N94" s="1" t="inlineStr">
         <is>
-          <t>L902: isolated marker/symbol line :: .</t>
+          <t>L863: symbol-only separator/garbage line :: 5.40</t>
         </is>
       </c>
       <c r="O94" s="1" t="inlineStr"/>
@@ -4936,7 +4808,7 @@
       <c r="M95" s="1" t="inlineStr"/>
       <c r="N95" s="1" t="inlineStr">
         <is>
-          <t>L903: symbol-only separator/garbage line :: 3.55</t>
+          <t>L864: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="O95" s="1" t="inlineStr"/>
@@ -4967,7 +4839,7 @@
       <c r="M96" s="1" t="inlineStr"/>
       <c r="N96" s="1" t="inlineStr">
         <is>
-          <t>L905: isolated marker/symbol line :: .</t>
+          <t>L865: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O96" s="1" t="inlineStr"/>
@@ -4998,7 +4870,7 @@
       <c r="M97" s="1" t="inlineStr"/>
       <c r="N97" s="1" t="inlineStr">
         <is>
-          <t>L907: isolated marker/symbol line :: 455</t>
+          <t>L866: symbol-only separator/garbage line :: 7.05</t>
         </is>
       </c>
       <c r="O97" s="1" t="inlineStr"/>
@@ -5029,7 +4901,7 @@
       <c r="M98" s="1" t="inlineStr"/>
       <c r="N98" s="1" t="inlineStr">
         <is>
-          <t>L910: symbol-only separator/garbage line :: 6.25</t>
+          <t>L867: isolated marker/symbol line :: “</t>
         </is>
       </c>
       <c r="O98" s="1" t="inlineStr"/>
@@ -5060,7 +4932,7 @@
       <c r="M99" s="1" t="inlineStr"/>
       <c r="N99" s="1" t="inlineStr">
         <is>
-          <t>L914: symbol-only separator/garbage line :: 6.55</t>
+          <t>L868: isolated marker/symbol line :: “</t>
         </is>
       </c>
       <c r="O99" s="1" t="inlineStr"/>
@@ -5091,7 +4963,7 @@
       <c r="M100" s="1" t="inlineStr"/>
       <c r="N100" s="1" t="inlineStr">
         <is>
-          <t>L917: symbol-only separator/garbage line :: 8.15</t>
+          <t>L870: symbol-only separator/garbage line :: 6.55</t>
         </is>
       </c>
       <c r="O100" s="1" t="inlineStr"/>
@@ -5122,7 +4994,7 @@
       <c r="M101" s="1" t="inlineStr"/>
       <c r="N101" s="1" t="inlineStr">
         <is>
-          <t>L918: isolated marker/symbol line :: "</t>
+          <t>L871: isolated marker/symbol line :: “</t>
         </is>
       </c>
       <c r="O101" s="1" t="inlineStr"/>
@@ -5153,7 +5025,7 @@
       <c r="M102" s="1" t="inlineStr"/>
       <c r="N102" s="1" t="inlineStr">
         <is>
-          <t>L921: symbol-only separator/garbage line :: 11.00</t>
+          <t>L872: isolated marker/symbol line :: “</t>
         </is>
       </c>
       <c r="O102" s="1" t="inlineStr"/>
@@ -5184,7 +5056,7 @@
       <c r="M103" s="1" t="inlineStr"/>
       <c r="N103" s="1" t="inlineStr">
         <is>
-          <t>L1004: isolated marker/symbol line :: A</t>
+          <t>L873: symbol-only separator/garbage line :: 8.10</t>
         </is>
       </c>
       <c r="O103" s="1" t="inlineStr"/>
@@ -5215,7 +5087,7 @@
       <c r="M104" s="1" t="inlineStr"/>
       <c r="N104" s="1" t="inlineStr">
         <is>
-          <t>L1005: isolated marker/symbol line :: 2</t>
+          <t>L874: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="O104" s="1" t="inlineStr"/>
@@ -5246,7 +5118,7 @@
       <c r="M105" s="1" t="inlineStr"/>
       <c r="N105" s="1" t="inlineStr">
         <is>
-          <t>L1120: isolated marker/symbol line :: &amp;</t>
+          <t>L875: isolated marker/symbol line :: "</t>
         </is>
       </c>
       <c r="O105" s="1" t="inlineStr"/>
@@ -5277,7 +5149,7 @@
       <c r="M106" s="1" t="inlineStr"/>
       <c r="N106" s="1" t="inlineStr">
         <is>
-          <t>L1123: isolated marker/symbol line :: 199</t>
+          <t>L877: symbol-only separator/garbage line :: 9.20</t>
         </is>
       </c>
       <c r="O106" s="1" t="inlineStr"/>
@@ -5308,7 +5180,7 @@
       <c r="M107" s="1" t="inlineStr"/>
       <c r="N107" s="1" t="inlineStr">
         <is>
-          <t>L1177: isolated marker/symbol line :: 7</t>
+          <t>L878: isolated marker/symbol line :: “</t>
         </is>
       </c>
       <c r="O107" s="1" t="inlineStr"/>
@@ -5339,7 +5211,7 @@
       <c r="M108" s="1" t="inlineStr"/>
       <c r="N108" s="1" t="inlineStr">
         <is>
-          <t>L1184: isolated marker/symbol line :: D</t>
+          <t>L879: isolated marker/symbol line :: “</t>
         </is>
       </c>
       <c r="O108" s="1" t="inlineStr"/>
@@ -5370,7 +5242,7 @@
       <c r="M109" s="1" t="inlineStr"/>
       <c r="N109" s="1" t="inlineStr">
         <is>
-          <t>L1192: isolated marker/symbol line :: 7</t>
+          <t>L880: symbol-only separator/garbage line :: 10.30</t>
         </is>
       </c>
       <c r="O109" s="1" t="inlineStr"/>
@@ -5401,7 +5273,7 @@
       <c r="M110" s="1" t="inlineStr"/>
       <c r="N110" s="1" t="inlineStr">
         <is>
-          <t>L1200: isolated marker/symbol line :: 1</t>
+          <t>L881: isolated marker/symbol line :: “</t>
         </is>
       </c>
       <c r="O110" s="1" t="inlineStr"/>
@@ -5432,7 +5304,7 @@
       <c r="M111" s="1" t="inlineStr"/>
       <c r="N111" s="1" t="inlineStr">
         <is>
-          <t>L1206: isolated marker/symbol line :: R</t>
+          <t>L882: isolated marker/symbol line :: “</t>
         </is>
       </c>
       <c r="O111" s="1" t="inlineStr"/>
@@ -5463,7 +5335,7 @@
       <c r="M112" s="1" t="inlineStr"/>
       <c r="N112" s="1" t="inlineStr">
         <is>
-          <t>L1243: stray/suspicious non-ASCII glyph(s): U+00AE REGISTERED SIGN | isolated marker/symbol line :: å®¶</t>
+          <t>L892: symbol-only separator/garbage line :: 8.45</t>
         </is>
       </c>
       <c r="O112" s="1" t="inlineStr"/>
@@ -5478,6 +5350,1060 @@
       <c r="X112" s="1" t="inlineStr"/>
       <c r="Y112" s="1" t="inlineStr"/>
     </row>
+    <row r="113">
+      <c r="A113" s="1" t="inlineStr"/>
+      <c r="B113" s="1" t="inlineStr"/>
+      <c r="C113" s="1" t="inlineStr"/>
+      <c r="D113" s="1" t="inlineStr"/>
+      <c r="E113" s="1" t="inlineStr"/>
+      <c r="F113" s="1" t="inlineStr"/>
+      <c r="G113" s="1" t="inlineStr"/>
+      <c r="H113" s="1" t="inlineStr"/>
+      <c r="I113" s="1" t="inlineStr"/>
+      <c r="J113" s="1" t="inlineStr"/>
+      <c r="K113" s="1" t="inlineStr"/>
+      <c r="L113" s="1" t="inlineStr"/>
+      <c r="M113" s="1" t="inlineStr"/>
+      <c r="N113" s="1" t="inlineStr">
+        <is>
+          <t>L893: isolated marker/symbol line :: 6</t>
+        </is>
+      </c>
+      <c r="O113" s="1" t="inlineStr"/>
+      <c r="P113" s="1" t="inlineStr"/>
+      <c r="Q113" s="1" t="inlineStr"/>
+      <c r="R113" s="1" t="inlineStr"/>
+      <c r="S113" s="1" t="inlineStr"/>
+      <c r="T113" s="1" t="inlineStr"/>
+      <c r="U113" s="1" t="inlineStr"/>
+      <c r="V113" s="1" t="inlineStr"/>
+      <c r="W113" s="1" t="inlineStr"/>
+      <c r="X113" s="1" t="inlineStr"/>
+      <c r="Y113" s="1" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="inlineStr"/>
+      <c r="B114" s="1" t="inlineStr"/>
+      <c r="C114" s="1" t="inlineStr"/>
+      <c r="D114" s="1" t="inlineStr"/>
+      <c r="E114" s="1" t="inlineStr"/>
+      <c r="F114" s="1" t="inlineStr"/>
+      <c r="G114" s="1" t="inlineStr"/>
+      <c r="H114" s="1" t="inlineStr"/>
+      <c r="I114" s="1" t="inlineStr"/>
+      <c r="J114" s="1" t="inlineStr"/>
+      <c r="K114" s="1" t="inlineStr"/>
+      <c r="L114" s="1" t="inlineStr"/>
+      <c r="M114" s="1" t="inlineStr"/>
+      <c r="N114" s="1" t="inlineStr">
+        <is>
+          <t>L894: symbol-only separator/garbage line :: 9.65</t>
+        </is>
+      </c>
+      <c r="O114" s="1" t="inlineStr"/>
+      <c r="P114" s="1" t="inlineStr"/>
+      <c r="Q114" s="1" t="inlineStr"/>
+      <c r="R114" s="1" t="inlineStr"/>
+      <c r="S114" s="1" t="inlineStr"/>
+      <c r="T114" s="1" t="inlineStr"/>
+      <c r="U114" s="1" t="inlineStr"/>
+      <c r="V114" s="1" t="inlineStr"/>
+      <c r="W114" s="1" t="inlineStr"/>
+      <c r="X114" s="1" t="inlineStr"/>
+      <c r="Y114" s="1" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="inlineStr"/>
+      <c r="B115" s="1" t="inlineStr"/>
+      <c r="C115" s="1" t="inlineStr"/>
+      <c r="D115" s="1" t="inlineStr"/>
+      <c r="E115" s="1" t="inlineStr"/>
+      <c r="F115" s="1" t="inlineStr"/>
+      <c r="G115" s="1" t="inlineStr"/>
+      <c r="H115" s="1" t="inlineStr"/>
+      <c r="I115" s="1" t="inlineStr"/>
+      <c r="J115" s="1" t="inlineStr"/>
+      <c r="K115" s="1" t="inlineStr"/>
+      <c r="L115" s="1" t="inlineStr"/>
+      <c r="M115" s="1" t="inlineStr"/>
+      <c r="N115" s="1" t="inlineStr">
+        <is>
+          <t>L895: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
+        </is>
+      </c>
+      <c r="O115" s="1" t="inlineStr"/>
+      <c r="P115" s="1" t="inlineStr"/>
+      <c r="Q115" s="1" t="inlineStr"/>
+      <c r="R115" s="1" t="inlineStr"/>
+      <c r="S115" s="1" t="inlineStr"/>
+      <c r="T115" s="1" t="inlineStr"/>
+      <c r="U115" s="1" t="inlineStr"/>
+      <c r="V115" s="1" t="inlineStr"/>
+      <c r="W115" s="1" t="inlineStr"/>
+      <c r="X115" s="1" t="inlineStr"/>
+      <c r="Y115" s="1" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="inlineStr"/>
+      <c r="B116" s="1" t="inlineStr"/>
+      <c r="C116" s="1" t="inlineStr"/>
+      <c r="D116" s="1" t="inlineStr"/>
+      <c r="E116" s="1" t="inlineStr"/>
+      <c r="F116" s="1" t="inlineStr"/>
+      <c r="G116" s="1" t="inlineStr"/>
+      <c r="H116" s="1" t="inlineStr"/>
+      <c r="I116" s="1" t="inlineStr"/>
+      <c r="J116" s="1" t="inlineStr"/>
+      <c r="K116" s="1" t="inlineStr"/>
+      <c r="L116" s="1" t="inlineStr"/>
+      <c r="M116" s="1" t="inlineStr"/>
+      <c r="N116" s="1" t="inlineStr">
+        <is>
+          <t>L900: symbol-only separator/garbage line :: 2.50</t>
+        </is>
+      </c>
+      <c r="O116" s="1" t="inlineStr"/>
+      <c r="P116" s="1" t="inlineStr"/>
+      <c r="Q116" s="1" t="inlineStr"/>
+      <c r="R116" s="1" t="inlineStr"/>
+      <c r="S116" s="1" t="inlineStr"/>
+      <c r="T116" s="1" t="inlineStr"/>
+      <c r="U116" s="1" t="inlineStr"/>
+      <c r="V116" s="1" t="inlineStr"/>
+      <c r="W116" s="1" t="inlineStr"/>
+      <c r="X116" s="1" t="inlineStr"/>
+      <c r="Y116" s="1" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="inlineStr"/>
+      <c r="B117" s="1" t="inlineStr"/>
+      <c r="C117" s="1" t="inlineStr"/>
+      <c r="D117" s="1" t="inlineStr"/>
+      <c r="E117" s="1" t="inlineStr"/>
+      <c r="F117" s="1" t="inlineStr"/>
+      <c r="G117" s="1" t="inlineStr"/>
+      <c r="H117" s="1" t="inlineStr"/>
+      <c r="I117" s="1" t="inlineStr"/>
+      <c r="J117" s="1" t="inlineStr"/>
+      <c r="K117" s="1" t="inlineStr"/>
+      <c r="L117" s="1" t="inlineStr"/>
+      <c r="M117" s="1" t="inlineStr"/>
+      <c r="N117" s="1" t="inlineStr">
+        <is>
+          <t>L901: isolated marker/symbol line :: “</t>
+        </is>
+      </c>
+      <c r="O117" s="1" t="inlineStr"/>
+      <c r="P117" s="1" t="inlineStr"/>
+      <c r="Q117" s="1" t="inlineStr"/>
+      <c r="R117" s="1" t="inlineStr"/>
+      <c r="S117" s="1" t="inlineStr"/>
+      <c r="T117" s="1" t="inlineStr"/>
+      <c r="U117" s="1" t="inlineStr"/>
+      <c r="V117" s="1" t="inlineStr"/>
+      <c r="W117" s="1" t="inlineStr"/>
+      <c r="X117" s="1" t="inlineStr"/>
+      <c r="Y117" s="1" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="inlineStr"/>
+      <c r="B118" s="1" t="inlineStr"/>
+      <c r="C118" s="1" t="inlineStr"/>
+      <c r="D118" s="1" t="inlineStr"/>
+      <c r="E118" s="1" t="inlineStr"/>
+      <c r="F118" s="1" t="inlineStr"/>
+      <c r="G118" s="1" t="inlineStr"/>
+      <c r="H118" s="1" t="inlineStr"/>
+      <c r="I118" s="1" t="inlineStr"/>
+      <c r="J118" s="1" t="inlineStr"/>
+      <c r="K118" s="1" t="inlineStr"/>
+      <c r="L118" s="1" t="inlineStr"/>
+      <c r="M118" s="1" t="inlineStr"/>
+      <c r="N118" s="1" t="inlineStr">
+        <is>
+          <t>L902: isolated marker/symbol line :: .</t>
+        </is>
+      </c>
+      <c r="O118" s="1" t="inlineStr"/>
+      <c r="P118" s="1" t="inlineStr"/>
+      <c r="Q118" s="1" t="inlineStr"/>
+      <c r="R118" s="1" t="inlineStr"/>
+      <c r="S118" s="1" t="inlineStr"/>
+      <c r="T118" s="1" t="inlineStr"/>
+      <c r="U118" s="1" t="inlineStr"/>
+      <c r="V118" s="1" t="inlineStr"/>
+      <c r="W118" s="1" t="inlineStr"/>
+      <c r="X118" s="1" t="inlineStr"/>
+      <c r="Y118" s="1" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="inlineStr"/>
+      <c r="B119" s="1" t="inlineStr"/>
+      <c r="C119" s="1" t="inlineStr"/>
+      <c r="D119" s="1" t="inlineStr"/>
+      <c r="E119" s="1" t="inlineStr"/>
+      <c r="F119" s="1" t="inlineStr"/>
+      <c r="G119" s="1" t="inlineStr"/>
+      <c r="H119" s="1" t="inlineStr"/>
+      <c r="I119" s="1" t="inlineStr"/>
+      <c r="J119" s="1" t="inlineStr"/>
+      <c r="K119" s="1" t="inlineStr"/>
+      <c r="L119" s="1" t="inlineStr"/>
+      <c r="M119" s="1" t="inlineStr"/>
+      <c r="N119" s="1" t="inlineStr">
+        <is>
+          <t>L903: symbol-only separator/garbage line :: 3.55</t>
+        </is>
+      </c>
+      <c r="O119" s="1" t="inlineStr"/>
+      <c r="P119" s="1" t="inlineStr"/>
+      <c r="Q119" s="1" t="inlineStr"/>
+      <c r="R119" s="1" t="inlineStr"/>
+      <c r="S119" s="1" t="inlineStr"/>
+      <c r="T119" s="1" t="inlineStr"/>
+      <c r="U119" s="1" t="inlineStr"/>
+      <c r="V119" s="1" t="inlineStr"/>
+      <c r="W119" s="1" t="inlineStr"/>
+      <c r="X119" s="1" t="inlineStr"/>
+      <c r="Y119" s="1" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="inlineStr"/>
+      <c r="B120" s="1" t="inlineStr"/>
+      <c r="C120" s="1" t="inlineStr"/>
+      <c r="D120" s="1" t="inlineStr"/>
+      <c r="E120" s="1" t="inlineStr"/>
+      <c r="F120" s="1" t="inlineStr"/>
+      <c r="G120" s="1" t="inlineStr"/>
+      <c r="H120" s="1" t="inlineStr"/>
+      <c r="I120" s="1" t="inlineStr"/>
+      <c r="J120" s="1" t="inlineStr"/>
+      <c r="K120" s="1" t="inlineStr"/>
+      <c r="L120" s="1" t="inlineStr"/>
+      <c r="M120" s="1" t="inlineStr"/>
+      <c r="N120" s="1" t="inlineStr">
+        <is>
+          <t>L904: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
+        </is>
+      </c>
+      <c r="O120" s="1" t="inlineStr"/>
+      <c r="P120" s="1" t="inlineStr"/>
+      <c r="Q120" s="1" t="inlineStr"/>
+      <c r="R120" s="1" t="inlineStr"/>
+      <c r="S120" s="1" t="inlineStr"/>
+      <c r="T120" s="1" t="inlineStr"/>
+      <c r="U120" s="1" t="inlineStr"/>
+      <c r="V120" s="1" t="inlineStr"/>
+      <c r="W120" s="1" t="inlineStr"/>
+      <c r="X120" s="1" t="inlineStr"/>
+      <c r="Y120" s="1" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="inlineStr"/>
+      <c r="B121" s="1" t="inlineStr"/>
+      <c r="C121" s="1" t="inlineStr"/>
+      <c r="D121" s="1" t="inlineStr"/>
+      <c r="E121" s="1" t="inlineStr"/>
+      <c r="F121" s="1" t="inlineStr"/>
+      <c r="G121" s="1" t="inlineStr"/>
+      <c r="H121" s="1" t="inlineStr"/>
+      <c r="I121" s="1" t="inlineStr"/>
+      <c r="J121" s="1" t="inlineStr"/>
+      <c r="K121" s="1" t="inlineStr"/>
+      <c r="L121" s="1" t="inlineStr"/>
+      <c r="M121" s="1" t="inlineStr"/>
+      <c r="N121" s="1" t="inlineStr">
+        <is>
+          <t>L905: isolated marker/symbol line :: .</t>
+        </is>
+      </c>
+      <c r="O121" s="1" t="inlineStr"/>
+      <c r="P121" s="1" t="inlineStr"/>
+      <c r="Q121" s="1" t="inlineStr"/>
+      <c r="R121" s="1" t="inlineStr"/>
+      <c r="S121" s="1" t="inlineStr"/>
+      <c r="T121" s="1" t="inlineStr"/>
+      <c r="U121" s="1" t="inlineStr"/>
+      <c r="V121" s="1" t="inlineStr"/>
+      <c r="W121" s="1" t="inlineStr"/>
+      <c r="X121" s="1" t="inlineStr"/>
+      <c r="Y121" s="1" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="inlineStr"/>
+      <c r="B122" s="1" t="inlineStr"/>
+      <c r="C122" s="1" t="inlineStr"/>
+      <c r="D122" s="1" t="inlineStr"/>
+      <c r="E122" s="1" t="inlineStr"/>
+      <c r="F122" s="1" t="inlineStr"/>
+      <c r="G122" s="1" t="inlineStr"/>
+      <c r="H122" s="1" t="inlineStr"/>
+      <c r="I122" s="1" t="inlineStr"/>
+      <c r="J122" s="1" t="inlineStr"/>
+      <c r="K122" s="1" t="inlineStr"/>
+      <c r="L122" s="1" t="inlineStr"/>
+      <c r="M122" s="1" t="inlineStr"/>
+      <c r="N122" s="1" t="inlineStr">
+        <is>
+          <t>L907: isolated marker/symbol line :: 455</t>
+        </is>
+      </c>
+      <c r="O122" s="1" t="inlineStr"/>
+      <c r="P122" s="1" t="inlineStr"/>
+      <c r="Q122" s="1" t="inlineStr"/>
+      <c r="R122" s="1" t="inlineStr"/>
+      <c r="S122" s="1" t="inlineStr"/>
+      <c r="T122" s="1" t="inlineStr"/>
+      <c r="U122" s="1" t="inlineStr"/>
+      <c r="V122" s="1" t="inlineStr"/>
+      <c r="W122" s="1" t="inlineStr"/>
+      <c r="X122" s="1" t="inlineStr"/>
+      <c r="Y122" s="1" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="inlineStr"/>
+      <c r="B123" s="1" t="inlineStr"/>
+      <c r="C123" s="1" t="inlineStr"/>
+      <c r="D123" s="1" t="inlineStr"/>
+      <c r="E123" s="1" t="inlineStr"/>
+      <c r="F123" s="1" t="inlineStr"/>
+      <c r="G123" s="1" t="inlineStr"/>
+      <c r="H123" s="1" t="inlineStr"/>
+      <c r="I123" s="1" t="inlineStr"/>
+      <c r="J123" s="1" t="inlineStr"/>
+      <c r="K123" s="1" t="inlineStr"/>
+      <c r="L123" s="1" t="inlineStr"/>
+      <c r="M123" s="1" t="inlineStr"/>
+      <c r="N123" s="1" t="inlineStr">
+        <is>
+          <t>L908: isolated marker/symbol line :: “</t>
+        </is>
+      </c>
+      <c r="O123" s="1" t="inlineStr"/>
+      <c r="P123" s="1" t="inlineStr"/>
+      <c r="Q123" s="1" t="inlineStr"/>
+      <c r="R123" s="1" t="inlineStr"/>
+      <c r="S123" s="1" t="inlineStr"/>
+      <c r="T123" s="1" t="inlineStr"/>
+      <c r="U123" s="1" t="inlineStr"/>
+      <c r="V123" s="1" t="inlineStr"/>
+      <c r="W123" s="1" t="inlineStr"/>
+      <c r="X123" s="1" t="inlineStr"/>
+      <c r="Y123" s="1" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="inlineStr"/>
+      <c r="B124" s="1" t="inlineStr"/>
+      <c r="C124" s="1" t="inlineStr"/>
+      <c r="D124" s="1" t="inlineStr"/>
+      <c r="E124" s="1" t="inlineStr"/>
+      <c r="F124" s="1" t="inlineStr"/>
+      <c r="G124" s="1" t="inlineStr"/>
+      <c r="H124" s="1" t="inlineStr"/>
+      <c r="I124" s="1" t="inlineStr"/>
+      <c r="J124" s="1" t="inlineStr"/>
+      <c r="K124" s="1" t="inlineStr"/>
+      <c r="L124" s="1" t="inlineStr"/>
+      <c r="M124" s="1" t="inlineStr"/>
+      <c r="N124" s="1" t="inlineStr">
+        <is>
+          <t>L909: isolated marker/symbol line :: “</t>
+        </is>
+      </c>
+      <c r="O124" s="1" t="inlineStr"/>
+      <c r="P124" s="1" t="inlineStr"/>
+      <c r="Q124" s="1" t="inlineStr"/>
+      <c r="R124" s="1" t="inlineStr"/>
+      <c r="S124" s="1" t="inlineStr"/>
+      <c r="T124" s="1" t="inlineStr"/>
+      <c r="U124" s="1" t="inlineStr"/>
+      <c r="V124" s="1" t="inlineStr"/>
+      <c r="W124" s="1" t="inlineStr"/>
+      <c r="X124" s="1" t="inlineStr"/>
+      <c r="Y124" s="1" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="inlineStr"/>
+      <c r="B125" s="1" t="inlineStr"/>
+      <c r="C125" s="1" t="inlineStr"/>
+      <c r="D125" s="1" t="inlineStr"/>
+      <c r="E125" s="1" t="inlineStr"/>
+      <c r="F125" s="1" t="inlineStr"/>
+      <c r="G125" s="1" t="inlineStr"/>
+      <c r="H125" s="1" t="inlineStr"/>
+      <c r="I125" s="1" t="inlineStr"/>
+      <c r="J125" s="1" t="inlineStr"/>
+      <c r="K125" s="1" t="inlineStr"/>
+      <c r="L125" s="1" t="inlineStr"/>
+      <c r="M125" s="1" t="inlineStr"/>
+      <c r="N125" s="1" t="inlineStr">
+        <is>
+          <t>L910: symbol-only separator/garbage line :: 6.25</t>
+        </is>
+      </c>
+      <c r="O125" s="1" t="inlineStr"/>
+      <c r="P125" s="1" t="inlineStr"/>
+      <c r="Q125" s="1" t="inlineStr"/>
+      <c r="R125" s="1" t="inlineStr"/>
+      <c r="S125" s="1" t="inlineStr"/>
+      <c r="T125" s="1" t="inlineStr"/>
+      <c r="U125" s="1" t="inlineStr"/>
+      <c r="V125" s="1" t="inlineStr"/>
+      <c r="W125" s="1" t="inlineStr"/>
+      <c r="X125" s="1" t="inlineStr"/>
+      <c r="Y125" s="1" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="inlineStr"/>
+      <c r="B126" s="1" t="inlineStr"/>
+      <c r="C126" s="1" t="inlineStr"/>
+      <c r="D126" s="1" t="inlineStr"/>
+      <c r="E126" s="1" t="inlineStr"/>
+      <c r="F126" s="1" t="inlineStr"/>
+      <c r="G126" s="1" t="inlineStr"/>
+      <c r="H126" s="1" t="inlineStr"/>
+      <c r="I126" s="1" t="inlineStr"/>
+      <c r="J126" s="1" t="inlineStr"/>
+      <c r="K126" s="1" t="inlineStr"/>
+      <c r="L126" s="1" t="inlineStr"/>
+      <c r="M126" s="1" t="inlineStr"/>
+      <c r="N126" s="1" t="inlineStr">
+        <is>
+          <t>L911: isolated marker/symbol line :: “</t>
+        </is>
+      </c>
+      <c r="O126" s="1" t="inlineStr"/>
+      <c r="P126" s="1" t="inlineStr"/>
+      <c r="Q126" s="1" t="inlineStr"/>
+      <c r="R126" s="1" t="inlineStr"/>
+      <c r="S126" s="1" t="inlineStr"/>
+      <c r="T126" s="1" t="inlineStr"/>
+      <c r="U126" s="1" t="inlineStr"/>
+      <c r="V126" s="1" t="inlineStr"/>
+      <c r="W126" s="1" t="inlineStr"/>
+      <c r="X126" s="1" t="inlineStr"/>
+      <c r="Y126" s="1" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="inlineStr"/>
+      <c r="B127" s="1" t="inlineStr"/>
+      <c r="C127" s="1" t="inlineStr"/>
+      <c r="D127" s="1" t="inlineStr"/>
+      <c r="E127" s="1" t="inlineStr"/>
+      <c r="F127" s="1" t="inlineStr"/>
+      <c r="G127" s="1" t="inlineStr"/>
+      <c r="H127" s="1" t="inlineStr"/>
+      <c r="I127" s="1" t="inlineStr"/>
+      <c r="J127" s="1" t="inlineStr"/>
+      <c r="K127" s="1" t="inlineStr"/>
+      <c r="L127" s="1" t="inlineStr"/>
+      <c r="M127" s="1" t="inlineStr"/>
+      <c r="N127" s="1" t="inlineStr">
+        <is>
+          <t>L912: isolated marker/symbol line :: “</t>
+        </is>
+      </c>
+      <c r="O127" s="1" t="inlineStr"/>
+      <c r="P127" s="1" t="inlineStr"/>
+      <c r="Q127" s="1" t="inlineStr"/>
+      <c r="R127" s="1" t="inlineStr"/>
+      <c r="S127" s="1" t="inlineStr"/>
+      <c r="T127" s="1" t="inlineStr"/>
+      <c r="U127" s="1" t="inlineStr"/>
+      <c r="V127" s="1" t="inlineStr"/>
+      <c r="W127" s="1" t="inlineStr"/>
+      <c r="X127" s="1" t="inlineStr"/>
+      <c r="Y127" s="1" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="inlineStr"/>
+      <c r="B128" s="1" t="inlineStr"/>
+      <c r="C128" s="1" t="inlineStr"/>
+      <c r="D128" s="1" t="inlineStr"/>
+      <c r="E128" s="1" t="inlineStr"/>
+      <c r="F128" s="1" t="inlineStr"/>
+      <c r="G128" s="1" t="inlineStr"/>
+      <c r="H128" s="1" t="inlineStr"/>
+      <c r="I128" s="1" t="inlineStr"/>
+      <c r="J128" s="1" t="inlineStr"/>
+      <c r="K128" s="1" t="inlineStr"/>
+      <c r="L128" s="1" t="inlineStr"/>
+      <c r="M128" s="1" t="inlineStr"/>
+      <c r="N128" s="1" t="inlineStr">
+        <is>
+          <t>L914: symbol-only separator/garbage line :: 6.55</t>
+        </is>
+      </c>
+      <c r="O128" s="1" t="inlineStr"/>
+      <c r="P128" s="1" t="inlineStr"/>
+      <c r="Q128" s="1" t="inlineStr"/>
+      <c r="R128" s="1" t="inlineStr"/>
+      <c r="S128" s="1" t="inlineStr"/>
+      <c r="T128" s="1" t="inlineStr"/>
+      <c r="U128" s="1" t="inlineStr"/>
+      <c r="V128" s="1" t="inlineStr"/>
+      <c r="W128" s="1" t="inlineStr"/>
+      <c r="X128" s="1" t="inlineStr"/>
+      <c r="Y128" s="1" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="inlineStr"/>
+      <c r="B129" s="1" t="inlineStr"/>
+      <c r="C129" s="1" t="inlineStr"/>
+      <c r="D129" s="1" t="inlineStr"/>
+      <c r="E129" s="1" t="inlineStr"/>
+      <c r="F129" s="1" t="inlineStr"/>
+      <c r="G129" s="1" t="inlineStr"/>
+      <c r="H129" s="1" t="inlineStr"/>
+      <c r="I129" s="1" t="inlineStr"/>
+      <c r="J129" s="1" t="inlineStr"/>
+      <c r="K129" s="1" t="inlineStr"/>
+      <c r="L129" s="1" t="inlineStr"/>
+      <c r="M129" s="1" t="inlineStr"/>
+      <c r="N129" s="1" t="inlineStr">
+        <is>
+          <t>L915: isolated marker/symbol line :: “</t>
+        </is>
+      </c>
+      <c r="O129" s="1" t="inlineStr"/>
+      <c r="P129" s="1" t="inlineStr"/>
+      <c r="Q129" s="1" t="inlineStr"/>
+      <c r="R129" s="1" t="inlineStr"/>
+      <c r="S129" s="1" t="inlineStr"/>
+      <c r="T129" s="1" t="inlineStr"/>
+      <c r="U129" s="1" t="inlineStr"/>
+      <c r="V129" s="1" t="inlineStr"/>
+      <c r="W129" s="1" t="inlineStr"/>
+      <c r="X129" s="1" t="inlineStr"/>
+      <c r="Y129" s="1" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="inlineStr"/>
+      <c r="B130" s="1" t="inlineStr"/>
+      <c r="C130" s="1" t="inlineStr"/>
+      <c r="D130" s="1" t="inlineStr"/>
+      <c r="E130" s="1" t="inlineStr"/>
+      <c r="F130" s="1" t="inlineStr"/>
+      <c r="G130" s="1" t="inlineStr"/>
+      <c r="H130" s="1" t="inlineStr"/>
+      <c r="I130" s="1" t="inlineStr"/>
+      <c r="J130" s="1" t="inlineStr"/>
+      <c r="K130" s="1" t="inlineStr"/>
+      <c r="L130" s="1" t="inlineStr"/>
+      <c r="M130" s="1" t="inlineStr"/>
+      <c r="N130" s="1" t="inlineStr">
+        <is>
+          <t>L916: isolated marker/symbol line :: “</t>
+        </is>
+      </c>
+      <c r="O130" s="1" t="inlineStr"/>
+      <c r="P130" s="1" t="inlineStr"/>
+      <c r="Q130" s="1" t="inlineStr"/>
+      <c r="R130" s="1" t="inlineStr"/>
+      <c r="S130" s="1" t="inlineStr"/>
+      <c r="T130" s="1" t="inlineStr"/>
+      <c r="U130" s="1" t="inlineStr"/>
+      <c r="V130" s="1" t="inlineStr"/>
+      <c r="W130" s="1" t="inlineStr"/>
+      <c r="X130" s="1" t="inlineStr"/>
+      <c r="Y130" s="1" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="inlineStr"/>
+      <c r="B131" s="1" t="inlineStr"/>
+      <c r="C131" s="1" t="inlineStr"/>
+      <c r="D131" s="1" t="inlineStr"/>
+      <c r="E131" s="1" t="inlineStr"/>
+      <c r="F131" s="1" t="inlineStr"/>
+      <c r="G131" s="1" t="inlineStr"/>
+      <c r="H131" s="1" t="inlineStr"/>
+      <c r="I131" s="1" t="inlineStr"/>
+      <c r="J131" s="1" t="inlineStr"/>
+      <c r="K131" s="1" t="inlineStr"/>
+      <c r="L131" s="1" t="inlineStr"/>
+      <c r="M131" s="1" t="inlineStr"/>
+      <c r="N131" s="1" t="inlineStr">
+        <is>
+          <t>L917: symbol-only separator/garbage line :: 8.15</t>
+        </is>
+      </c>
+      <c r="O131" s="1" t="inlineStr"/>
+      <c r="P131" s="1" t="inlineStr"/>
+      <c r="Q131" s="1" t="inlineStr"/>
+      <c r="R131" s="1" t="inlineStr"/>
+      <c r="S131" s="1" t="inlineStr"/>
+      <c r="T131" s="1" t="inlineStr"/>
+      <c r="U131" s="1" t="inlineStr"/>
+      <c r="V131" s="1" t="inlineStr"/>
+      <c r="W131" s="1" t="inlineStr"/>
+      <c r="X131" s="1" t="inlineStr"/>
+      <c r="Y131" s="1" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="inlineStr"/>
+      <c r="B132" s="1" t="inlineStr"/>
+      <c r="C132" s="1" t="inlineStr"/>
+      <c r="D132" s="1" t="inlineStr"/>
+      <c r="E132" s="1" t="inlineStr"/>
+      <c r="F132" s="1" t="inlineStr"/>
+      <c r="G132" s="1" t="inlineStr"/>
+      <c r="H132" s="1" t="inlineStr"/>
+      <c r="I132" s="1" t="inlineStr"/>
+      <c r="J132" s="1" t="inlineStr"/>
+      <c r="K132" s="1" t="inlineStr"/>
+      <c r="L132" s="1" t="inlineStr"/>
+      <c r="M132" s="1" t="inlineStr"/>
+      <c r="N132" s="1" t="inlineStr">
+        <is>
+          <t>L918: isolated marker/symbol line :: "</t>
+        </is>
+      </c>
+      <c r="O132" s="1" t="inlineStr"/>
+      <c r="P132" s="1" t="inlineStr"/>
+      <c r="Q132" s="1" t="inlineStr"/>
+      <c r="R132" s="1" t="inlineStr"/>
+      <c r="S132" s="1" t="inlineStr"/>
+      <c r="T132" s="1" t="inlineStr"/>
+      <c r="U132" s="1" t="inlineStr"/>
+      <c r="V132" s="1" t="inlineStr"/>
+      <c r="W132" s="1" t="inlineStr"/>
+      <c r="X132" s="1" t="inlineStr"/>
+      <c r="Y132" s="1" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="inlineStr"/>
+      <c r="B133" s="1" t="inlineStr"/>
+      <c r="C133" s="1" t="inlineStr"/>
+      <c r="D133" s="1" t="inlineStr"/>
+      <c r="E133" s="1" t="inlineStr"/>
+      <c r="F133" s="1" t="inlineStr"/>
+      <c r="G133" s="1" t="inlineStr"/>
+      <c r="H133" s="1" t="inlineStr"/>
+      <c r="I133" s="1" t="inlineStr"/>
+      <c r="J133" s="1" t="inlineStr"/>
+      <c r="K133" s="1" t="inlineStr"/>
+      <c r="L133" s="1" t="inlineStr"/>
+      <c r="M133" s="1" t="inlineStr"/>
+      <c r="N133" s="1" t="inlineStr">
+        <is>
+          <t>L919: isolated marker/symbol line :: “</t>
+        </is>
+      </c>
+      <c r="O133" s="1" t="inlineStr"/>
+      <c r="P133" s="1" t="inlineStr"/>
+      <c r="Q133" s="1" t="inlineStr"/>
+      <c r="R133" s="1" t="inlineStr"/>
+      <c r="S133" s="1" t="inlineStr"/>
+      <c r="T133" s="1" t="inlineStr"/>
+      <c r="U133" s="1" t="inlineStr"/>
+      <c r="V133" s="1" t="inlineStr"/>
+      <c r="W133" s="1" t="inlineStr"/>
+      <c r="X133" s="1" t="inlineStr"/>
+      <c r="Y133" s="1" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="inlineStr"/>
+      <c r="B134" s="1" t="inlineStr"/>
+      <c r="C134" s="1" t="inlineStr"/>
+      <c r="D134" s="1" t="inlineStr"/>
+      <c r="E134" s="1" t="inlineStr"/>
+      <c r="F134" s="1" t="inlineStr"/>
+      <c r="G134" s="1" t="inlineStr"/>
+      <c r="H134" s="1" t="inlineStr"/>
+      <c r="I134" s="1" t="inlineStr"/>
+      <c r="J134" s="1" t="inlineStr"/>
+      <c r="K134" s="1" t="inlineStr"/>
+      <c r="L134" s="1" t="inlineStr"/>
+      <c r="M134" s="1" t="inlineStr"/>
+      <c r="N134" s="1" t="inlineStr">
+        <is>
+          <t>L921: symbol-only separator/garbage line :: 11.00</t>
+        </is>
+      </c>
+      <c r="O134" s="1" t="inlineStr"/>
+      <c r="P134" s="1" t="inlineStr"/>
+      <c r="Q134" s="1" t="inlineStr"/>
+      <c r="R134" s="1" t="inlineStr"/>
+      <c r="S134" s="1" t="inlineStr"/>
+      <c r="T134" s="1" t="inlineStr"/>
+      <c r="U134" s="1" t="inlineStr"/>
+      <c r="V134" s="1" t="inlineStr"/>
+      <c r="W134" s="1" t="inlineStr"/>
+      <c r="X134" s="1" t="inlineStr"/>
+      <c r="Y134" s="1" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="inlineStr"/>
+      <c r="B135" s="1" t="inlineStr"/>
+      <c r="C135" s="1" t="inlineStr"/>
+      <c r="D135" s="1" t="inlineStr"/>
+      <c r="E135" s="1" t="inlineStr"/>
+      <c r="F135" s="1" t="inlineStr"/>
+      <c r="G135" s="1" t="inlineStr"/>
+      <c r="H135" s="1" t="inlineStr"/>
+      <c r="I135" s="1" t="inlineStr"/>
+      <c r="J135" s="1" t="inlineStr"/>
+      <c r="K135" s="1" t="inlineStr"/>
+      <c r="L135" s="1" t="inlineStr"/>
+      <c r="M135" s="1" t="inlineStr"/>
+      <c r="N135" s="1" t="inlineStr">
+        <is>
+          <t>L922: isolated marker/symbol line :: “</t>
+        </is>
+      </c>
+      <c r="O135" s="1" t="inlineStr"/>
+      <c r="P135" s="1" t="inlineStr"/>
+      <c r="Q135" s="1" t="inlineStr"/>
+      <c r="R135" s="1" t="inlineStr"/>
+      <c r="S135" s="1" t="inlineStr"/>
+      <c r="T135" s="1" t="inlineStr"/>
+      <c r="U135" s="1" t="inlineStr"/>
+      <c r="V135" s="1" t="inlineStr"/>
+      <c r="W135" s="1" t="inlineStr"/>
+      <c r="X135" s="1" t="inlineStr"/>
+      <c r="Y135" s="1" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="inlineStr"/>
+      <c r="B136" s="1" t="inlineStr"/>
+      <c r="C136" s="1" t="inlineStr"/>
+      <c r="D136" s="1" t="inlineStr"/>
+      <c r="E136" s="1" t="inlineStr"/>
+      <c r="F136" s="1" t="inlineStr"/>
+      <c r="G136" s="1" t="inlineStr"/>
+      <c r="H136" s="1" t="inlineStr"/>
+      <c r="I136" s="1" t="inlineStr"/>
+      <c r="J136" s="1" t="inlineStr"/>
+      <c r="K136" s="1" t="inlineStr"/>
+      <c r="L136" s="1" t="inlineStr"/>
+      <c r="M136" s="1" t="inlineStr"/>
+      <c r="N136" s="1" t="inlineStr">
+        <is>
+          <t>L923: isolated marker/symbol line :: “</t>
+        </is>
+      </c>
+      <c r="O136" s="1" t="inlineStr"/>
+      <c r="P136" s="1" t="inlineStr"/>
+      <c r="Q136" s="1" t="inlineStr"/>
+      <c r="R136" s="1" t="inlineStr"/>
+      <c r="S136" s="1" t="inlineStr"/>
+      <c r="T136" s="1" t="inlineStr"/>
+      <c r="U136" s="1" t="inlineStr"/>
+      <c r="V136" s="1" t="inlineStr"/>
+      <c r="W136" s="1" t="inlineStr"/>
+      <c r="X136" s="1" t="inlineStr"/>
+      <c r="Y136" s="1" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="inlineStr"/>
+      <c r="B137" s="1" t="inlineStr"/>
+      <c r="C137" s="1" t="inlineStr"/>
+      <c r="D137" s="1" t="inlineStr"/>
+      <c r="E137" s="1" t="inlineStr"/>
+      <c r="F137" s="1" t="inlineStr"/>
+      <c r="G137" s="1" t="inlineStr"/>
+      <c r="H137" s="1" t="inlineStr"/>
+      <c r="I137" s="1" t="inlineStr"/>
+      <c r="J137" s="1" t="inlineStr"/>
+      <c r="K137" s="1" t="inlineStr"/>
+      <c r="L137" s="1" t="inlineStr"/>
+      <c r="M137" s="1" t="inlineStr"/>
+      <c r="N137" s="1" t="inlineStr">
+        <is>
+          <t>L1004: isolated marker/symbol line :: A</t>
+        </is>
+      </c>
+      <c r="O137" s="1" t="inlineStr"/>
+      <c r="P137" s="1" t="inlineStr"/>
+      <c r="Q137" s="1" t="inlineStr"/>
+      <c r="R137" s="1" t="inlineStr"/>
+      <c r="S137" s="1" t="inlineStr"/>
+      <c r="T137" s="1" t="inlineStr"/>
+      <c r="U137" s="1" t="inlineStr"/>
+      <c r="V137" s="1" t="inlineStr"/>
+      <c r="W137" s="1" t="inlineStr"/>
+      <c r="X137" s="1" t="inlineStr"/>
+      <c r="Y137" s="1" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="inlineStr"/>
+      <c r="B138" s="1" t="inlineStr"/>
+      <c r="C138" s="1" t="inlineStr"/>
+      <c r="D138" s="1" t="inlineStr"/>
+      <c r="E138" s="1" t="inlineStr"/>
+      <c r="F138" s="1" t="inlineStr"/>
+      <c r="G138" s="1" t="inlineStr"/>
+      <c r="H138" s="1" t="inlineStr"/>
+      <c r="I138" s="1" t="inlineStr"/>
+      <c r="J138" s="1" t="inlineStr"/>
+      <c r="K138" s="1" t="inlineStr"/>
+      <c r="L138" s="1" t="inlineStr"/>
+      <c r="M138" s="1" t="inlineStr"/>
+      <c r="N138" s="1" t="inlineStr">
+        <is>
+          <t>L1005: isolated marker/symbol line :: 2</t>
+        </is>
+      </c>
+      <c r="O138" s="1" t="inlineStr"/>
+      <c r="P138" s="1" t="inlineStr"/>
+      <c r="Q138" s="1" t="inlineStr"/>
+      <c r="R138" s="1" t="inlineStr"/>
+      <c r="S138" s="1" t="inlineStr"/>
+      <c r="T138" s="1" t="inlineStr"/>
+      <c r="U138" s="1" t="inlineStr"/>
+      <c r="V138" s="1" t="inlineStr"/>
+      <c r="W138" s="1" t="inlineStr"/>
+      <c r="X138" s="1" t="inlineStr"/>
+      <c r="Y138" s="1" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="inlineStr"/>
+      <c r="B139" s="1" t="inlineStr"/>
+      <c r="C139" s="1" t="inlineStr"/>
+      <c r="D139" s="1" t="inlineStr"/>
+      <c r="E139" s="1" t="inlineStr"/>
+      <c r="F139" s="1" t="inlineStr"/>
+      <c r="G139" s="1" t="inlineStr"/>
+      <c r="H139" s="1" t="inlineStr"/>
+      <c r="I139" s="1" t="inlineStr"/>
+      <c r="J139" s="1" t="inlineStr"/>
+      <c r="K139" s="1" t="inlineStr"/>
+      <c r="L139" s="1" t="inlineStr"/>
+      <c r="M139" s="1" t="inlineStr"/>
+      <c r="N139" s="1" t="inlineStr">
+        <is>
+          <t>L1120: isolated marker/symbol line :: &amp;</t>
+        </is>
+      </c>
+      <c r="O139" s="1" t="inlineStr"/>
+      <c r="P139" s="1" t="inlineStr"/>
+      <c r="Q139" s="1" t="inlineStr"/>
+      <c r="R139" s="1" t="inlineStr"/>
+      <c r="S139" s="1" t="inlineStr"/>
+      <c r="T139" s="1" t="inlineStr"/>
+      <c r="U139" s="1" t="inlineStr"/>
+      <c r="V139" s="1" t="inlineStr"/>
+      <c r="W139" s="1" t="inlineStr"/>
+      <c r="X139" s="1" t="inlineStr"/>
+      <c r="Y139" s="1" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="inlineStr"/>
+      <c r="B140" s="1" t="inlineStr"/>
+      <c r="C140" s="1" t="inlineStr"/>
+      <c r="D140" s="1" t="inlineStr"/>
+      <c r="E140" s="1" t="inlineStr"/>
+      <c r="F140" s="1" t="inlineStr"/>
+      <c r="G140" s="1" t="inlineStr"/>
+      <c r="H140" s="1" t="inlineStr"/>
+      <c r="I140" s="1" t="inlineStr"/>
+      <c r="J140" s="1" t="inlineStr"/>
+      <c r="K140" s="1" t="inlineStr"/>
+      <c r="L140" s="1" t="inlineStr"/>
+      <c r="M140" s="1" t="inlineStr"/>
+      <c r="N140" s="1" t="inlineStr">
+        <is>
+          <t>L1123: isolated marker/symbol line :: 199</t>
+        </is>
+      </c>
+      <c r="O140" s="1" t="inlineStr"/>
+      <c r="P140" s="1" t="inlineStr"/>
+      <c r="Q140" s="1" t="inlineStr"/>
+      <c r="R140" s="1" t="inlineStr"/>
+      <c r="S140" s="1" t="inlineStr"/>
+      <c r="T140" s="1" t="inlineStr"/>
+      <c r="U140" s="1" t="inlineStr"/>
+      <c r="V140" s="1" t="inlineStr"/>
+      <c r="W140" s="1" t="inlineStr"/>
+      <c r="X140" s="1" t="inlineStr"/>
+      <c r="Y140" s="1" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="inlineStr"/>
+      <c r="B141" s="1" t="inlineStr"/>
+      <c r="C141" s="1" t="inlineStr"/>
+      <c r="D141" s="1" t="inlineStr"/>
+      <c r="E141" s="1" t="inlineStr"/>
+      <c r="F141" s="1" t="inlineStr"/>
+      <c r="G141" s="1" t="inlineStr"/>
+      <c r="H141" s="1" t="inlineStr"/>
+      <c r="I141" s="1" t="inlineStr"/>
+      <c r="J141" s="1" t="inlineStr"/>
+      <c r="K141" s="1" t="inlineStr"/>
+      <c r="L141" s="1" t="inlineStr"/>
+      <c r="M141" s="1" t="inlineStr"/>
+      <c r="N141" s="1" t="inlineStr">
+        <is>
+          <t>L1177: isolated marker/symbol line :: 7</t>
+        </is>
+      </c>
+      <c r="O141" s="1" t="inlineStr"/>
+      <c r="P141" s="1" t="inlineStr"/>
+      <c r="Q141" s="1" t="inlineStr"/>
+      <c r="R141" s="1" t="inlineStr"/>
+      <c r="S141" s="1" t="inlineStr"/>
+      <c r="T141" s="1" t="inlineStr"/>
+      <c r="U141" s="1" t="inlineStr"/>
+      <c r="V141" s="1" t="inlineStr"/>
+      <c r="W141" s="1" t="inlineStr"/>
+      <c r="X141" s="1" t="inlineStr"/>
+      <c r="Y141" s="1" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="inlineStr"/>
+      <c r="B142" s="1" t="inlineStr"/>
+      <c r="C142" s="1" t="inlineStr"/>
+      <c r="D142" s="1" t="inlineStr"/>
+      <c r="E142" s="1" t="inlineStr"/>
+      <c r="F142" s="1" t="inlineStr"/>
+      <c r="G142" s="1" t="inlineStr"/>
+      <c r="H142" s="1" t="inlineStr"/>
+      <c r="I142" s="1" t="inlineStr"/>
+      <c r="J142" s="1" t="inlineStr"/>
+      <c r="K142" s="1" t="inlineStr"/>
+      <c r="L142" s="1" t="inlineStr"/>
+      <c r="M142" s="1" t="inlineStr"/>
+      <c r="N142" s="1" t="inlineStr">
+        <is>
+          <t>L1184: isolated marker/symbol line :: D</t>
+        </is>
+      </c>
+      <c r="O142" s="1" t="inlineStr"/>
+      <c r="P142" s="1" t="inlineStr"/>
+      <c r="Q142" s="1" t="inlineStr"/>
+      <c r="R142" s="1" t="inlineStr"/>
+      <c r="S142" s="1" t="inlineStr"/>
+      <c r="T142" s="1" t="inlineStr"/>
+      <c r="U142" s="1" t="inlineStr"/>
+      <c r="V142" s="1" t="inlineStr"/>
+      <c r="W142" s="1" t="inlineStr"/>
+      <c r="X142" s="1" t="inlineStr"/>
+      <c r="Y142" s="1" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="inlineStr"/>
+      <c r="B143" s="1" t="inlineStr"/>
+      <c r="C143" s="1" t="inlineStr"/>
+      <c r="D143" s="1" t="inlineStr"/>
+      <c r="E143" s="1" t="inlineStr"/>
+      <c r="F143" s="1" t="inlineStr"/>
+      <c r="G143" s="1" t="inlineStr"/>
+      <c r="H143" s="1" t="inlineStr"/>
+      <c r="I143" s="1" t="inlineStr"/>
+      <c r="J143" s="1" t="inlineStr"/>
+      <c r="K143" s="1" t="inlineStr"/>
+      <c r="L143" s="1" t="inlineStr"/>
+      <c r="M143" s="1" t="inlineStr"/>
+      <c r="N143" s="1" t="inlineStr">
+        <is>
+          <t>L1192: isolated marker/symbol line :: 7</t>
+        </is>
+      </c>
+      <c r="O143" s="1" t="inlineStr"/>
+      <c r="P143" s="1" t="inlineStr"/>
+      <c r="Q143" s="1" t="inlineStr"/>
+      <c r="R143" s="1" t="inlineStr"/>
+      <c r="S143" s="1" t="inlineStr"/>
+      <c r="T143" s="1" t="inlineStr"/>
+      <c r="U143" s="1" t="inlineStr"/>
+      <c r="V143" s="1" t="inlineStr"/>
+      <c r="W143" s="1" t="inlineStr"/>
+      <c r="X143" s="1" t="inlineStr"/>
+      <c r="Y143" s="1" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="inlineStr"/>
+      <c r="B144" s="1" t="inlineStr"/>
+      <c r="C144" s="1" t="inlineStr"/>
+      <c r="D144" s="1" t="inlineStr"/>
+      <c r="E144" s="1" t="inlineStr"/>
+      <c r="F144" s="1" t="inlineStr"/>
+      <c r="G144" s="1" t="inlineStr"/>
+      <c r="H144" s="1" t="inlineStr"/>
+      <c r="I144" s="1" t="inlineStr"/>
+      <c r="J144" s="1" t="inlineStr"/>
+      <c r="K144" s="1" t="inlineStr"/>
+      <c r="L144" s="1" t="inlineStr"/>
+      <c r="M144" s="1" t="inlineStr"/>
+      <c r="N144" s="1" t="inlineStr">
+        <is>
+          <t>L1200: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
+      <c r="O144" s="1" t="inlineStr"/>
+      <c r="P144" s="1" t="inlineStr"/>
+      <c r="Q144" s="1" t="inlineStr"/>
+      <c r="R144" s="1" t="inlineStr"/>
+      <c r="S144" s="1" t="inlineStr"/>
+      <c r="T144" s="1" t="inlineStr"/>
+      <c r="U144" s="1" t="inlineStr"/>
+      <c r="V144" s="1" t="inlineStr"/>
+      <c r="W144" s="1" t="inlineStr"/>
+      <c r="X144" s="1" t="inlineStr"/>
+      <c r="Y144" s="1" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="inlineStr"/>
+      <c r="B145" s="1" t="inlineStr"/>
+      <c r="C145" s="1" t="inlineStr"/>
+      <c r="D145" s="1" t="inlineStr"/>
+      <c r="E145" s="1" t="inlineStr"/>
+      <c r="F145" s="1" t="inlineStr"/>
+      <c r="G145" s="1" t="inlineStr"/>
+      <c r="H145" s="1" t="inlineStr"/>
+      <c r="I145" s="1" t="inlineStr"/>
+      <c r="J145" s="1" t="inlineStr"/>
+      <c r="K145" s="1" t="inlineStr"/>
+      <c r="L145" s="1" t="inlineStr"/>
+      <c r="M145" s="1" t="inlineStr"/>
+      <c r="N145" s="1" t="inlineStr">
+        <is>
+          <t>L1206: isolated marker/symbol line :: R</t>
+        </is>
+      </c>
+      <c r="O145" s="1" t="inlineStr"/>
+      <c r="P145" s="1" t="inlineStr"/>
+      <c r="Q145" s="1" t="inlineStr"/>
+      <c r="R145" s="1" t="inlineStr"/>
+      <c r="S145" s="1" t="inlineStr"/>
+      <c r="T145" s="1" t="inlineStr"/>
+      <c r="U145" s="1" t="inlineStr"/>
+      <c r="V145" s="1" t="inlineStr"/>
+      <c r="W145" s="1" t="inlineStr"/>
+      <c r="X145" s="1" t="inlineStr"/>
+      <c r="Y145" s="1" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="inlineStr"/>
+      <c r="B146" s="1" t="inlineStr"/>
+      <c r="C146" s="1" t="inlineStr"/>
+      <c r="D146" s="1" t="inlineStr"/>
+      <c r="E146" s="1" t="inlineStr"/>
+      <c r="F146" s="1" t="inlineStr"/>
+      <c r="G146" s="1" t="inlineStr"/>
+      <c r="H146" s="1" t="inlineStr"/>
+      <c r="I146" s="1" t="inlineStr"/>
+      <c r="J146" s="1" t="inlineStr"/>
+      <c r="K146" s="1" t="inlineStr"/>
+      <c r="L146" s="1" t="inlineStr"/>
+      <c r="M146" s="1" t="inlineStr"/>
+      <c r="N146" s="1" t="inlineStr">
+        <is>
+          <t>L1243: stray/suspicious non-ASCII glyph(s): U+5BB6 CJK UNIFIED IDEOGRAPH-5BB6 | isolated marker/symbol line :: 家</t>
+        </is>
+      </c>
+      <c r="O146" s="1" t="inlineStr"/>
+      <c r="P146" s="1" t="inlineStr"/>
+      <c r="Q146" s="1" t="inlineStr"/>
+      <c r="R146" s="1" t="inlineStr"/>
+      <c r="S146" s="1" t="inlineStr"/>
+      <c r="T146" s="1" t="inlineStr"/>
+      <c r="U146" s="1" t="inlineStr"/>
+      <c r="V146" s="1" t="inlineStr"/>
+      <c r="W146" s="1" t="inlineStr"/>
+      <c r="X146" s="1" t="inlineStr"/>
+      <c r="Y146" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
